--- a/data-source/ordens.xlsx
+++ b/data-source/ordens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/prompt-smart-stock-sight (4) (1)antig/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_A83E0076CB385EDFDA183BCB61CCBEC488860D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CB16885-290C-4F68-9CDD-785B0B5D8242}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_A83E0076CB385EDFDA183BCB61CCBEC488860D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C20B8A6-5C83-48C1-B994-E611390773A3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="62">
   <si>
     <t>Nro.OP</t>
   </si>
@@ -106,9 +106,6 @@
     <t>BORGONHA OURO LIGHT</t>
   </si>
   <si>
-    <t>GRID CANELA</t>
-  </si>
-  <si>
     <t>JUMBO 1</t>
   </si>
   <si>
@@ -118,61 +115,100 @@
     <t>LILLY MANTEIGA</t>
   </si>
   <si>
-    <t>NAPA METAL LYON OURO ROSADO</t>
-  </si>
-  <si>
     <t>BORGONHA PRATA</t>
   </si>
   <si>
-    <t>BORGONHA BROWN</t>
-  </si>
-  <si>
-    <t>CANYON CANELA</t>
-  </si>
-  <si>
     <t>NAPA BARI FOSCO CARAMELO</t>
   </si>
   <si>
-    <t>SAVOY GLAM PRATA</t>
-  </si>
-  <si>
-    <t>BORGONHA PRETO</t>
-  </si>
-  <si>
     <t>METALIZADO LAS VEGAS OURO LIGHT</t>
   </si>
   <si>
-    <t>TRANSFE</t>
-  </si>
-  <si>
-    <t>OPHIDIA METAL OURO LIGHT</t>
-  </si>
-  <si>
     <t>SAVOY GLAM OURO LIGHT</t>
   </si>
   <si>
-    <t>FLORENZA BEGE</t>
-  </si>
-  <si>
-    <t>NAPA MADRID CASTOR - PU 0.9MM</t>
-  </si>
-  <si>
     <t>BERGAMO CARAMELO</t>
   </si>
   <si>
-    <t>ESTAM</t>
-  </si>
-  <si>
-    <t>LILLY NUDE</t>
-  </si>
-  <si>
-    <t>NAPA MADRID BEGE - PU 0.9MM</t>
-  </si>
-  <si>
     <t>NAPA BARI FOSCO CAFE</t>
   </si>
   <si>
-    <t>DOHA GRAFITE</t>
+    <t>MIRAGE OURO ROSADO</t>
+  </si>
+  <si>
+    <t>CANYON LIMONCELLO</t>
+  </si>
+  <si>
+    <t>RECOB</t>
+  </si>
+  <si>
+    <t>LILLY OFF WHITE</t>
+  </si>
+  <si>
+    <t>GR 1</t>
+  </si>
+  <si>
+    <t>CORDOBA BEGE</t>
+  </si>
+  <si>
+    <t>NAPA BARI FOSCO OFF WHITE</t>
+  </si>
+  <si>
+    <t>NAPA BARI FOSCO BEGE</t>
+  </si>
+  <si>
+    <t>BERGAMO NATURAL</t>
+  </si>
+  <si>
+    <t>DENVER PRETO</t>
+  </si>
+  <si>
+    <t>LILLY ROSE</t>
+  </si>
+  <si>
+    <t>MERIDA PRETO</t>
+  </si>
+  <si>
+    <t>NAPA FLOATER VENEZIA DOURADO</t>
+  </si>
+  <si>
+    <t>SORRENTO OFF WHITE</t>
+  </si>
+  <si>
+    <t>LENNY MANTEIGA</t>
+  </si>
+  <si>
+    <t>TWIST METAL BELLINI/MAGENTA</t>
+  </si>
+  <si>
+    <t>MIRAGE OURO LIGHT</t>
+  </si>
+  <si>
+    <t>MACKAY GLAM OURO LIGHT</t>
+  </si>
+  <si>
+    <t>ASPEN PRATA</t>
+  </si>
+  <si>
+    <t>ASPEN OURO LIGHT</t>
+  </si>
+  <si>
+    <t>ASPEN GRAFITE</t>
+  </si>
+  <si>
+    <t>ASPEN BRONZE</t>
+  </si>
+  <si>
+    <t>ASPEN WHISKY</t>
+  </si>
+  <si>
+    <t>SALERNO LIMONCELLO</t>
+  </si>
+  <si>
+    <t>ASPEN BROWN</t>
+  </si>
+  <si>
+    <t>MACKAY GLAM GRAFITE</t>
   </si>
 </sst>
 </file>
@@ -181,7 +217,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[Blue]###########0;[Red]\-###########0"/>
-    <numFmt numFmtId="166" formatCode="[Blue]###,###,###,##0.000;[Red]\-###,###,###,##0.000"/>
+    <numFmt numFmtId="165" formatCode="[Blue]###,###,###,##0.000;[Red]\-###,###,###,##0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -243,7 +279,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -582,7 +618,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" customWidth="1"/>
@@ -685,25 +721,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>6911</v>
+        <v>6876</v>
       </c>
       <c r="B4" s="2">
-        <v>14180</v>
+        <v>15535</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2">
         <v>39</v>
       </c>
       <c r="E4" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="4">
-        <v>132</v>
+        <v>186.5</v>
       </c>
       <c r="G4" s="5">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="H4" s="2">
         <v>10</v>
@@ -714,13 +750,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>6937</v>
+        <v>6911</v>
       </c>
       <c r="B5" s="2">
-        <v>12879</v>
+        <v>14180</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2">
         <v>39</v>
@@ -729,27 +765,27 @@
         <v>40</v>
       </c>
       <c r="F5" s="4">
-        <v>240</v>
+        <v>132</v>
       </c>
       <c r="G5" s="5">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="H5" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>6938</v>
+        <v>6937</v>
       </c>
       <c r="B6" s="2">
-        <v>12883</v>
+        <v>12879</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2">
         <v>39</v>
@@ -772,13 +808,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>6939</v>
+        <v>6938</v>
       </c>
       <c r="B7" s="2">
-        <v>12776</v>
+        <v>12883</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2">
         <v>39</v>
@@ -801,13 +837,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>6940</v>
+        <v>6939</v>
       </c>
       <c r="B8" s="2">
-        <v>12878</v>
+        <v>12776</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="2">
         <v>39</v>
@@ -830,25 +866,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>7025</v>
+        <v>6940</v>
       </c>
       <c r="B9" s="2">
-        <v>17416</v>
+        <v>12878</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2">
         <v>39</v>
       </c>
       <c r="E9" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="4">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G9" s="5">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -859,13 +895,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>7425</v>
+        <v>7025</v>
       </c>
       <c r="B10" s="2">
-        <v>16633</v>
+        <v>17416</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="2">
         <v>39</v>
@@ -874,27 +910,27 @@
         <v>41</v>
       </c>
       <c r="F10" s="4">
-        <v>187.5</v>
+        <v>120</v>
       </c>
       <c r="G10" s="5">
-        <v>46230</v>
+        <v>46199</v>
       </c>
       <c r="H10" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>7427</v>
+        <v>7425</v>
       </c>
       <c r="B11" s="2">
-        <v>16477</v>
+        <v>16633</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="2">
         <v>39</v>
@@ -903,27 +939,27 @@
         <v>41</v>
       </c>
       <c r="F11" s="4">
-        <v>600</v>
+        <v>187.5</v>
       </c>
       <c r="G11" s="5">
         <v>46230</v>
       </c>
       <c r="H11" s="2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>7489</v>
+        <v>7427</v>
       </c>
       <c r="B12" s="2">
-        <v>9000183</v>
+        <v>16477</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D12" s="2">
         <v>39</v>
@@ -932,27 +968,27 @@
         <v>41</v>
       </c>
       <c r="F12" s="4">
-        <v>84</v>
+        <v>600</v>
       </c>
       <c r="G12" s="5">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="H12" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>7513</v>
+        <v>7428</v>
       </c>
       <c r="B13" s="2">
-        <v>17231</v>
+        <v>16475</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D13" s="2">
         <v>39</v>
@@ -961,27 +997,27 @@
         <v>41</v>
       </c>
       <c r="F13" s="4">
-        <v>520.5</v>
+        <v>400</v>
       </c>
       <c r="G13" s="5">
-        <v>46232</v>
+        <v>46230</v>
       </c>
       <c r="H13" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>7545</v>
+        <v>7489</v>
       </c>
       <c r="B14" s="2">
-        <v>15371</v>
+        <v>9000183</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D14" s="2">
         <v>39</v>
@@ -990,39 +1026,39 @@
         <v>41</v>
       </c>
       <c r="F14" s="4">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="G14" s="5">
-        <v>46233</v>
+        <v>46223</v>
       </c>
       <c r="H14" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>7604</v>
+        <v>7623</v>
       </c>
       <c r="B15" s="2">
-        <v>11843</v>
+        <v>12398</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2">
         <v>39</v>
       </c>
       <c r="E15" s="2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F15" s="4">
-        <v>77.5</v>
+        <v>115</v>
       </c>
       <c r="G15" s="5">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="H15" s="2">
         <v>10</v>
@@ -1033,10 +1069,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>7623</v>
+        <v>7624</v>
       </c>
       <c r="B16" s="2">
-        <v>12398</v>
+        <v>12399</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>29</v>
@@ -1048,27 +1084,27 @@
         <v>41</v>
       </c>
       <c r="F16" s="4">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="G16" s="5">
         <v>46240</v>
       </c>
       <c r="H16" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>7624</v>
+        <v>7809</v>
       </c>
       <c r="B17" s="2">
-        <v>12399</v>
+        <v>16466</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D17" s="2">
         <v>39</v>
@@ -1077,27 +1113,27 @@
         <v>41</v>
       </c>
       <c r="F17" s="4">
-        <v>200</v>
+        <v>94</v>
       </c>
       <c r="G17" s="5">
-        <v>46240</v>
+        <v>46253</v>
       </c>
       <c r="H17" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>7674</v>
+        <v>7834</v>
       </c>
       <c r="B18" s="2">
-        <v>17744</v>
+        <v>11845</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D18" s="2">
         <v>39</v>
@@ -1106,10 +1142,10 @@
         <v>41</v>
       </c>
       <c r="F18" s="4">
-        <v>202.5</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>46240</v>
+        <v>46255</v>
       </c>
       <c r="H18" s="2">
         <v>10</v>
@@ -1120,13 +1156,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>7687</v>
+        <v>7837</v>
       </c>
       <c r="B19" s="2">
-        <v>17420</v>
+        <v>9000134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D19" s="2">
         <v>39</v>
@@ -1135,27 +1171,27 @@
         <v>41</v>
       </c>
       <c r="F19" s="4">
-        <v>1000</v>
+        <v>8.5</v>
       </c>
       <c r="G19" s="5">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="H19" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>7688</v>
+        <v>7912</v>
       </c>
       <c r="B20" s="2">
         <v>11844</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D20" s="2">
         <v>39</v>
@@ -1164,27 +1200,27 @@
         <v>0</v>
       </c>
       <c r="F20" s="4">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G20" s="5">
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="H20" s="2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>7692</v>
+        <v>7913</v>
       </c>
       <c r="B21" s="2">
-        <v>16503</v>
+        <v>12400</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D21" s="2">
         <v>39</v>
@@ -1193,56 +1229,56 @@
         <v>41</v>
       </c>
       <c r="F21" s="4">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="G21" s="5">
-        <v>46247</v>
+        <v>46260</v>
       </c>
       <c r="H21" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>7693</v>
+        <v>7914</v>
       </c>
       <c r="B22" s="2">
-        <v>14789</v>
+        <v>17420</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="2">
+        <v>39</v>
+      </c>
+      <c r="E22" s="2">
+        <v>41</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="5">
+        <v>46260</v>
+      </c>
+      <c r="H22" s="2">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D22" s="2">
-        <v>39</v>
-      </c>
-      <c r="E22" s="2">
-        <v>41</v>
-      </c>
-      <c r="F22" s="4">
-        <v>400</v>
-      </c>
-      <c r="G22" s="5">
-        <v>46247</v>
-      </c>
-      <c r="H22" s="2">
-        <v>13</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>7808</v>
+        <v>7934</v>
       </c>
       <c r="B23" s="2">
-        <v>16577</v>
+        <v>13167</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D23" s="2">
         <v>39</v>
@@ -1254,24 +1290,24 @@
         <v>400</v>
       </c>
       <c r="G23" s="5">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="H23" s="2">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>7809</v>
+        <v>7990</v>
       </c>
       <c r="B24" s="2">
-        <v>16466</v>
+        <v>16737</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D24" s="2">
         <v>39</v>
@@ -1283,24 +1319,24 @@
         <v>1000</v>
       </c>
       <c r="G24" s="5">
-        <v>46253</v>
+        <v>46265</v>
       </c>
       <c r="H24" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>7820</v>
+        <v>7991</v>
       </c>
       <c r="B25" s="2">
-        <v>900019</v>
+        <v>16650</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D25" s="2">
         <v>39</v>
@@ -1309,10 +1345,10 @@
         <v>41</v>
       </c>
       <c r="F25" s="4">
-        <v>152</v>
+        <v>2000</v>
       </c>
       <c r="G25" s="5">
-        <v>46253</v>
+        <v>46265</v>
       </c>
       <c r="H25" s="2">
         <v>6</v>
@@ -1323,13 +1359,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>7834</v>
+        <v>7992</v>
       </c>
       <c r="B26" s="2">
-        <v>11845</v>
+        <v>16644</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D26" s="2">
         <v>39</v>
@@ -1341,21 +1377,21 @@
         <v>1000</v>
       </c>
       <c r="G26" s="5">
-        <v>46255</v>
+        <v>46265</v>
       </c>
       <c r="H26" s="2">
         <v>13</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>7837</v>
+        <v>7993</v>
       </c>
       <c r="B27" s="2">
-        <v>11907</v>
+        <v>16643</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>43</v>
@@ -1364,13 +1400,13 @@
         <v>39</v>
       </c>
       <c r="E27" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F27" s="4">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="G27" s="5">
-        <v>46253</v>
+        <v>46265</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
@@ -1381,13 +1417,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>7837</v>
+        <v>7995</v>
       </c>
       <c r="B28" s="2">
-        <v>9000134</v>
+        <v>17231</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D28" s="2">
         <v>39</v>
@@ -1396,27 +1432,27 @@
         <v>41</v>
       </c>
       <c r="F28" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G28" s="5">
-        <v>46253</v>
+        <v>46265</v>
       </c>
       <c r="H28" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>7871</v>
+        <v>7996</v>
       </c>
       <c r="B29" s="2">
-        <v>12550</v>
+        <v>6411</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D29" s="2">
         <v>39</v>
@@ -1428,24 +1464,24 @@
         <v>200</v>
       </c>
       <c r="G29" s="5">
-        <v>46253</v>
+        <v>46265</v>
       </c>
       <c r="H29" s="2">
         <v>13</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>7889</v>
+        <v>7997</v>
       </c>
       <c r="B30" s="2">
-        <v>30096</v>
+        <v>11845</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D30" s="2">
         <v>39</v>
@@ -1454,39 +1490,39 @@
         <v>41</v>
       </c>
       <c r="F30" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G30" s="5">
-        <v>46255</v>
+        <v>46265</v>
       </c>
       <c r="H30" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>7891</v>
+        <v>7998</v>
       </c>
       <c r="B31" s="2">
-        <v>11903</v>
+        <v>17420</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D31" s="2">
         <v>39</v>
       </c>
       <c r="E31" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F31" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G31" s="5">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="H31" s="2">
         <v>0</v>
@@ -1497,42 +1533,42 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>7895</v>
+        <v>7999</v>
       </c>
       <c r="B32" s="2">
-        <v>11903</v>
+        <v>17425</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D32" s="2">
         <v>39</v>
       </c>
       <c r="E32" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F32" s="4">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="G32" s="5">
-        <v>46252</v>
+        <v>46265</v>
       </c>
       <c r="H32" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>7899</v>
+        <v>8000</v>
       </c>
       <c r="B33" s="2">
-        <v>16650</v>
+        <v>17416</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D33" s="2">
         <v>39</v>
@@ -1541,27 +1577,27 @@
         <v>41</v>
       </c>
       <c r="F33" s="4">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G33" s="5">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="H33" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>7900</v>
+        <v>8001</v>
       </c>
       <c r="B34" s="2">
-        <v>16737</v>
+        <v>15686</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D34" s="2">
         <v>39</v>
@@ -1573,24 +1609,24 @@
         <v>200</v>
       </c>
       <c r="G34" s="5">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="H34" s="2">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>7914</v>
+        <v>8002</v>
       </c>
       <c r="B35" s="2">
-        <v>17420</v>
+        <v>13708</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D35" s="2">
         <v>39</v>
@@ -1602,41 +1638,418 @@
         <v>1000</v>
       </c>
       <c r="G35" s="5">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="H35" s="2">
         <v>13</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>7924</v>
+        <v>8003</v>
       </c>
       <c r="B36" s="2">
-        <v>13154</v>
+        <v>16605</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="2">
+        <v>39</v>
+      </c>
+      <c r="E36" s="2">
+        <v>41</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G36" s="5">
+        <v>46265</v>
+      </c>
+      <c r="H36" s="2">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>8004</v>
+      </c>
+      <c r="B37">
+        <v>11779</v>
+      </c>
+      <c r="C37" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="2">
-        <v>39</v>
-      </c>
-      <c r="E36" s="2">
-        <v>41</v>
-      </c>
-      <c r="F36" s="4">
+      <c r="D37">
+        <v>39</v>
+      </c>
+      <c r="E37">
+        <v>41</v>
+      </c>
+      <c r="F37">
+        <v>400</v>
+      </c>
+      <c r="G37">
+        <v>46265</v>
+      </c>
+      <c r="H37">
+        <v>13</v>
+      </c>
+      <c r="I37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>8013</v>
+      </c>
+      <c r="B38">
+        <v>15360</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38">
+        <v>39</v>
+      </c>
+      <c r="E38">
+        <v>41</v>
+      </c>
+      <c r="F38">
+        <v>120</v>
+      </c>
+      <c r="G38">
+        <v>46262</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>8034</v>
+      </c>
+      <c r="B39">
+        <v>15727</v>
+      </c>
+      <c r="C39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39">
+        <v>39</v>
+      </c>
+      <c r="E39">
+        <v>41</v>
+      </c>
+      <c r="F39">
         <v>200</v>
       </c>
-      <c r="G36" s="5">
-        <v>46261</v>
-      </c>
-      <c r="H36" s="2">
-        <v>0</v>
-      </c>
-      <c r="I36" s="3" t="s">
+      <c r="G39">
+        <v>46265</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>8035</v>
+      </c>
+      <c r="B40">
+        <v>15534</v>
+      </c>
+      <c r="C40" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40">
+        <v>39</v>
+      </c>
+      <c r="E40">
+        <v>41</v>
+      </c>
+      <c r="F40">
+        <v>400</v>
+      </c>
+      <c r="G40">
+        <v>46265</v>
+      </c>
+      <c r="H40">
+        <v>13</v>
+      </c>
+      <c r="I40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>8043</v>
+      </c>
+      <c r="B41">
+        <v>17322</v>
+      </c>
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41">
+        <v>39</v>
+      </c>
+      <c r="E41">
+        <v>41</v>
+      </c>
+      <c r="F41">
+        <v>400</v>
+      </c>
+      <c r="G41">
+        <v>46265</v>
+      </c>
+      <c r="H41">
+        <v>2</v>
+      </c>
+      <c r="I41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>8046</v>
+      </c>
+      <c r="B42">
+        <v>17883</v>
+      </c>
+      <c r="C42" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42">
+        <v>39</v>
+      </c>
+      <c r="E42">
+        <v>41</v>
+      </c>
+      <c r="F42">
+        <v>200</v>
+      </c>
+      <c r="G42">
+        <v>46266</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>8047</v>
+      </c>
+      <c r="B43">
+        <v>17884</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43">
+        <v>39</v>
+      </c>
+      <c r="E43">
+        <v>41</v>
+      </c>
+      <c r="F43">
+        <v>200</v>
+      </c>
+      <c r="G43">
+        <v>46266</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>8048</v>
+      </c>
+      <c r="B44">
+        <v>17882</v>
+      </c>
+      <c r="C44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44">
+        <v>39</v>
+      </c>
+      <c r="E44">
+        <v>41</v>
+      </c>
+      <c r="F44">
+        <v>200</v>
+      </c>
+      <c r="G44">
+        <v>46266</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>8049</v>
+      </c>
+      <c r="B45">
+        <v>17881</v>
+      </c>
+      <c r="C45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45">
+        <v>39</v>
+      </c>
+      <c r="E45">
+        <v>41</v>
+      </c>
+      <c r="F45">
+        <v>200</v>
+      </c>
+      <c r="G45">
+        <v>46266</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>8050</v>
+      </c>
+      <c r="B46">
+        <v>17878</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46">
+        <v>39</v>
+      </c>
+      <c r="E46">
+        <v>41</v>
+      </c>
+      <c r="F46">
+        <v>200</v>
+      </c>
+      <c r="G46">
+        <v>46266</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>8051</v>
+      </c>
+      <c r="B47">
+        <v>15651</v>
+      </c>
+      <c r="C47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47">
+        <v>39</v>
+      </c>
+      <c r="E47">
+        <v>41</v>
+      </c>
+      <c r="F47">
+        <v>200</v>
+      </c>
+      <c r="G47">
+        <v>46274</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>8054</v>
+      </c>
+      <c r="B48">
+        <v>17890</v>
+      </c>
+      <c r="C48" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48">
+        <v>39</v>
+      </c>
+      <c r="E48">
+        <v>41</v>
+      </c>
+      <c r="F48">
+        <v>200</v>
+      </c>
+      <c r="G48">
+        <v>46266</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>8071</v>
+      </c>
+      <c r="B49">
+        <v>17323</v>
+      </c>
+      <c r="C49" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49">
+        <v>39</v>
+      </c>
+      <c r="E49">
+        <v>41</v>
+      </c>
+      <c r="F49">
+        <v>400</v>
+      </c>
+      <c r="G49">
+        <v>46268</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49" t="s">
         <v>16</v>
       </c>
     </row>

--- a/data-source/ordens.xlsx
+++ b/data-source/ordens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/prompt-smart-stock-sight (4) (1)antig/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_A83E0076CB385EDFDA183BCB61CCBEC488860D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C20B8A6-5C83-48C1-B994-E611390773A3}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_A83E0076CB385EDFDA183BCB61CCBEC488860D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{878B015C-473E-4BC0-936B-8B971B83D889}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="61">
   <si>
     <t>Nro.OP</t>
   </si>
@@ -118,24 +118,9 @@
     <t>BORGONHA PRATA</t>
   </si>
   <si>
-    <t>NAPA BARI FOSCO CARAMELO</t>
-  </si>
-  <si>
     <t>METALIZADO LAS VEGAS OURO LIGHT</t>
   </si>
   <si>
-    <t>SAVOY GLAM OURO LIGHT</t>
-  </si>
-  <si>
-    <t>BERGAMO CARAMELO</t>
-  </si>
-  <si>
-    <t>NAPA BARI FOSCO CAFE</t>
-  </si>
-  <si>
-    <t>MIRAGE OURO ROSADO</t>
-  </si>
-  <si>
     <t>CANYON LIMONCELLO</t>
   </si>
   <si>
@@ -151,12 +136,6 @@
     <t>CORDOBA BEGE</t>
   </si>
   <si>
-    <t>NAPA BARI FOSCO OFF WHITE</t>
-  </si>
-  <si>
-    <t>NAPA BARI FOSCO BEGE</t>
-  </si>
-  <si>
     <t>BERGAMO NATURAL</t>
   </si>
   <si>
@@ -178,9 +157,6 @@
     <t>LENNY MANTEIGA</t>
   </si>
   <si>
-    <t>TWIST METAL BELLINI/MAGENTA</t>
-  </si>
-  <si>
     <t>MIRAGE OURO LIGHT</t>
   </si>
   <si>
@@ -209,6 +185,27 @@
   </si>
   <si>
     <t>MACKAY GLAM GRAFITE</t>
+  </si>
+  <si>
+    <t>BORGONHA BROWN</t>
+  </si>
+  <si>
+    <t>BORGONHA TITANIO</t>
+  </si>
+  <si>
+    <t>BORGONHA BRONZE</t>
+  </si>
+  <si>
+    <t>DENVER CANELA</t>
+  </si>
+  <si>
+    <t>MIRAGE PRATA</t>
+  </si>
+  <si>
+    <t>BORGONHA GRAFITE</t>
+  </si>
+  <si>
+    <t>BORGONHA WHISKY</t>
   </si>
 </sst>
 </file>
@@ -618,18 +615,18 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" customWidth="1"/>
-    <col min="8" max="8" width="25.21875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -721,25 +718,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>6876</v>
+        <v>6911</v>
       </c>
       <c r="B4" s="2">
-        <v>15535</v>
+        <v>14180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2">
         <v>39</v>
       </c>
       <c r="E4" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4" s="4">
-        <v>186.5</v>
+        <v>132</v>
       </c>
       <c r="G4" s="5">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="H4" s="2">
         <v>10</v>
@@ -750,13 +747,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>6911</v>
+        <v>6937</v>
       </c>
       <c r="B5" s="2">
-        <v>14180</v>
+        <v>12879</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2">
         <v>39</v>
@@ -765,27 +762,27 @@
         <v>40</v>
       </c>
       <c r="F5" s="4">
-        <v>132</v>
+        <v>240</v>
       </c>
       <c r="G5" s="5">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="H5" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>6937</v>
+        <v>6938</v>
       </c>
       <c r="B6" s="2">
-        <v>12879</v>
+        <v>12883</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2">
         <v>39</v>
@@ -808,13 +805,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>6938</v>
+        <v>6939</v>
       </c>
       <c r="B7" s="2">
-        <v>12883</v>
+        <v>12776</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2">
         <v>39</v>
@@ -837,13 +834,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>6939</v>
+        <v>6940</v>
       </c>
       <c r="B8" s="2">
-        <v>12776</v>
+        <v>12878</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2">
         <v>39</v>
@@ -866,25 +863,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>6940</v>
+        <v>7025</v>
       </c>
       <c r="B9" s="2">
-        <v>12878</v>
+        <v>17416</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2">
         <v>39</v>
       </c>
       <c r="E9" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" s="4">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="G9" s="5">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -895,13 +892,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>7025</v>
+        <v>7425</v>
       </c>
       <c r="B10" s="2">
-        <v>17416</v>
+        <v>16633</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="2">
         <v>39</v>
@@ -910,27 +907,27 @@
         <v>41</v>
       </c>
       <c r="F10" s="4">
-        <v>120</v>
+        <v>187.5</v>
       </c>
       <c r="G10" s="5">
-        <v>46199</v>
+        <v>46230</v>
       </c>
       <c r="H10" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>7425</v>
+        <v>7427</v>
       </c>
       <c r="B11" s="2">
-        <v>16633</v>
+        <v>16477</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="2">
         <v>39</v>
@@ -939,27 +936,27 @@
         <v>41</v>
       </c>
       <c r="F11" s="4">
-        <v>187.5</v>
+        <v>600</v>
       </c>
       <c r="G11" s="5">
         <v>46230</v>
       </c>
       <c r="H11" s="2">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>7427</v>
+        <v>7428</v>
       </c>
       <c r="B12" s="2">
-        <v>16477</v>
+        <v>16475</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2">
         <v>39</v>
@@ -968,27 +965,27 @@
         <v>41</v>
       </c>
       <c r="F12" s="4">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G12" s="5">
         <v>46230</v>
       </c>
       <c r="H12" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>7428</v>
+        <v>7489</v>
       </c>
       <c r="B13" s="2">
-        <v>16475</v>
+        <v>9000183</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2">
         <v>39</v>
@@ -997,27 +994,27 @@
         <v>41</v>
       </c>
       <c r="F13" s="4">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="G13" s="5">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="H13" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>7489</v>
+        <v>7623</v>
       </c>
       <c r="B14" s="2">
-        <v>9000183</v>
+        <v>12398</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2">
         <v>39</v>
@@ -1026,27 +1023,27 @@
         <v>41</v>
       </c>
       <c r="F14" s="4">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G14" s="5">
-        <v>46223</v>
+        <v>46240</v>
       </c>
       <c r="H14" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>7623</v>
+        <v>7624</v>
       </c>
       <c r="B15" s="2">
-        <v>12398</v>
+        <v>12399</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2">
         <v>39</v>
@@ -1055,56 +1052,56 @@
         <v>41</v>
       </c>
       <c r="F15" s="4">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="G15" s="5">
         <v>46240</v>
       </c>
       <c r="H15" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>7624</v>
+        <v>7912</v>
       </c>
       <c r="B16" s="2">
-        <v>12399</v>
+        <v>11844</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="2">
         <v>39</v>
       </c>
       <c r="E16" s="2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G16" s="5">
-        <v>46240</v>
+        <v>46260</v>
       </c>
       <c r="H16" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>7809</v>
+        <v>7913</v>
       </c>
       <c r="B17" s="2">
-        <v>16466</v>
+        <v>12400</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" s="2">
         <v>39</v>
@@ -1113,27 +1110,27 @@
         <v>41</v>
       </c>
       <c r="F17" s="4">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="G17" s="5">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="H17" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>7834</v>
+        <v>7934</v>
       </c>
       <c r="B18" s="2">
-        <v>11845</v>
+        <v>13167</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D18" s="2">
         <v>39</v>
@@ -1142,27 +1139,27 @@
         <v>41</v>
       </c>
       <c r="F18" s="4">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G18" s="5">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="H18" s="2">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>7837</v>
+        <v>7996</v>
       </c>
       <c r="B19" s="2">
-        <v>9000134</v>
+        <v>6411</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D19" s="2">
         <v>39</v>
@@ -1171,56 +1168,56 @@
         <v>41</v>
       </c>
       <c r="F19" s="4">
-        <v>8.5</v>
+        <v>200</v>
       </c>
       <c r="G19" s="5">
-        <v>46253</v>
+        <v>46265</v>
       </c>
       <c r="H19" s="2">
+        <v>2</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>7912</v>
+        <v>7997</v>
       </c>
       <c r="B20" s="2">
-        <v>11844</v>
+        <v>11845</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D20" s="2">
         <v>39</v>
       </c>
       <c r="E20" s="2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F20" s="4">
         <v>1000</v>
       </c>
       <c r="G20" s="5">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>7913</v>
+        <v>7998</v>
       </c>
       <c r="B21" s="2">
-        <v>12400</v>
+        <v>17420</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D21" s="2">
         <v>39</v>
@@ -1229,27 +1226,27 @@
         <v>41</v>
       </c>
       <c r="F21" s="4">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="5">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="H21" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>7914</v>
+        <v>7999</v>
       </c>
       <c r="B22" s="2">
-        <v>17420</v>
+        <v>17425</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D22" s="2">
         <v>39</v>
@@ -1261,24 +1258,24 @@
         <v>1000</v>
       </c>
       <c r="G22" s="5">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="H22" s="2">
         <v>3</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>7934</v>
+        <v>8000</v>
       </c>
       <c r="B23" s="2">
-        <v>13167</v>
+        <v>17416</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2">
         <v>39</v>
@@ -1287,27 +1284,27 @@
         <v>41</v>
       </c>
       <c r="F23" s="4">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G23" s="5">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="H23" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>7990</v>
+        <v>8001</v>
       </c>
       <c r="B24" s="2">
-        <v>16737</v>
+        <v>15686</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D24" s="2">
         <v>39</v>
@@ -1316,27 +1313,27 @@
         <v>41</v>
       </c>
       <c r="F24" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G24" s="5">
         <v>46265</v>
       </c>
       <c r="H24" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>7991</v>
+        <v>8002</v>
       </c>
       <c r="B25" s="2">
-        <v>16650</v>
+        <v>13708</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D25" s="2">
         <v>39</v>
@@ -1345,27 +1342,27 @@
         <v>41</v>
       </c>
       <c r="F25" s="4">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="5">
         <v>46265</v>
       </c>
       <c r="H25" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>7992</v>
+        <v>8003</v>
       </c>
       <c r="B26" s="2">
-        <v>16644</v>
+        <v>16605</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" s="2">
         <v>39</v>
@@ -1380,21 +1377,21 @@
         <v>46265</v>
       </c>
       <c r="H26" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>7993</v>
+        <v>8004</v>
       </c>
       <c r="B27" s="2">
-        <v>16643</v>
+        <v>11779</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" s="2">
         <v>39</v>
@@ -1403,27 +1400,27 @@
         <v>41</v>
       </c>
       <c r="F27" s="4">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="G27" s="5">
         <v>46265</v>
       </c>
       <c r="H27" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>7995</v>
+        <v>8035</v>
       </c>
       <c r="B28" s="2">
-        <v>17231</v>
+        <v>15534</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D28" s="2">
         <v>39</v>
@@ -1432,27 +1429,27 @@
         <v>41</v>
       </c>
       <c r="F28" s="4">
-        <v>1000</v>
+        <v>270.5</v>
       </c>
       <c r="G28" s="5">
         <v>46265</v>
       </c>
       <c r="H28" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>7996</v>
+        <v>8043</v>
       </c>
       <c r="B29" s="2">
-        <v>6411</v>
+        <v>17322</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D29" s="2">
         <v>39</v>
@@ -1461,27 +1458,27 @@
         <v>41</v>
       </c>
       <c r="F29" s="4">
-        <v>200</v>
+        <v>395</v>
       </c>
       <c r="G29" s="5">
         <v>46265</v>
       </c>
       <c r="H29" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>7997</v>
+        <v>8046</v>
       </c>
       <c r="B30" s="2">
-        <v>11845</v>
+        <v>17883</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D30" s="2">
         <v>39</v>
@@ -1490,27 +1487,27 @@
         <v>41</v>
       </c>
       <c r="F30" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G30" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H30" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>7998</v>
+        <v>8047</v>
       </c>
       <c r="B31" s="2">
-        <v>17420</v>
+        <v>17884</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D31" s="2">
         <v>39</v>
@@ -1519,27 +1516,27 @@
         <v>41</v>
       </c>
       <c r="F31" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G31" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H31" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>7999</v>
+        <v>8048</v>
       </c>
       <c r="B32" s="2">
-        <v>17425</v>
+        <v>17882</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D32" s="2">
         <v>39</v>
@@ -1548,27 +1545,27 @@
         <v>41</v>
       </c>
       <c r="F32" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G32" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H32" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>8000</v>
+        <v>8049</v>
       </c>
       <c r="B33" s="2">
-        <v>17416</v>
+        <v>17881</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="D33" s="2">
         <v>39</v>
@@ -1577,27 +1574,27 @@
         <v>41</v>
       </c>
       <c r="F33" s="4">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="G33" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H33" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>8001</v>
+        <v>8050</v>
       </c>
       <c r="B34" s="2">
-        <v>15686</v>
+        <v>17878</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D34" s="2">
         <v>39</v>
@@ -1609,24 +1606,24 @@
         <v>200</v>
       </c>
       <c r="G34" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>8002</v>
+        <v>8051</v>
       </c>
       <c r="B35" s="2">
-        <v>13708</v>
+        <v>15651</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D35" s="2">
         <v>39</v>
@@ -1635,27 +1632,27 @@
         <v>41</v>
       </c>
       <c r="F35" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G35" s="5">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="H35" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>8003</v>
+        <v>8054</v>
       </c>
       <c r="B36" s="2">
-        <v>16605</v>
+        <v>17890</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D36" s="2">
         <v>39</v>
@@ -1664,393 +1661,451 @@
         <v>41</v>
       </c>
       <c r="F36" s="4">
+        <v>200</v>
+      </c>
+      <c r="G36" s="5">
+        <v>46266</v>
+      </c>
+      <c r="H36" s="2">
+        <v>3</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>8071</v>
+      </c>
+      <c r="B37" s="2">
+        <v>17323</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" s="2">
+        <v>39</v>
+      </c>
+      <c r="E37" s="2">
+        <v>41</v>
+      </c>
+      <c r="F37" s="4">
+        <v>400</v>
+      </c>
+      <c r="G37" s="5">
+        <v>46268</v>
+      </c>
+      <c r="H37" s="2">
+        <v>2</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>8091</v>
+      </c>
+      <c r="B38" s="2">
+        <v>11845</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="2">
+        <v>39</v>
+      </c>
+      <c r="E38" s="2">
+        <v>41</v>
+      </c>
+      <c r="F38" s="4">
+        <v>300</v>
+      </c>
+      <c r="G38" s="5">
+        <v>46275</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>8092</v>
+      </c>
+      <c r="B39" s="2">
+        <v>30096</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" s="2">
+        <v>39</v>
+      </c>
+      <c r="E39" s="2">
+        <v>41</v>
+      </c>
+      <c r="F39" s="4">
+        <v>600</v>
+      </c>
+      <c r="G39" s="5">
+        <v>46275</v>
+      </c>
+      <c r="H39" s="2">
+        <v>13</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>8093</v>
+      </c>
+      <c r="B40" s="2">
+        <v>15212</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="2">
+        <v>39</v>
+      </c>
+      <c r="E40" s="2">
+        <v>41</v>
+      </c>
+      <c r="F40" s="4">
+        <v>400</v>
+      </c>
+      <c r="G40" s="5">
+        <v>46275</v>
+      </c>
+      <c r="H40" s="2">
+        <v>13</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>8094</v>
+      </c>
+      <c r="B41" s="2">
+        <v>6395</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="2">
+        <v>39</v>
+      </c>
+      <c r="E41" s="2">
+        <v>41</v>
+      </c>
+      <c r="F41" s="4">
+        <v>300</v>
+      </c>
+      <c r="G41" s="5">
+        <v>46275</v>
+      </c>
+      <c r="H41" s="2">
+        <v>13</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>8095</v>
+      </c>
+      <c r="B42" s="2">
+        <v>17231</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" s="2">
+        <v>39</v>
+      </c>
+      <c r="E42" s="2">
+        <v>41</v>
+      </c>
+      <c r="F42" s="4">
         <v>1000</v>
       </c>
-      <c r="G36" s="5">
-        <v>46265</v>
-      </c>
-      <c r="H36" s="2">
-        <v>1</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>8004</v>
-      </c>
-      <c r="B37">
-        <v>11779</v>
-      </c>
-      <c r="C37" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37">
-        <v>39</v>
-      </c>
-      <c r="E37">
-        <v>41</v>
-      </c>
-      <c r="F37">
+      <c r="G42" s="5">
+        <v>46275</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>8096</v>
+      </c>
+      <c r="B43" s="2">
+        <v>17256</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="2">
+        <v>39</v>
+      </c>
+      <c r="E43" s="2">
+        <v>41</v>
+      </c>
+      <c r="F43" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G43" s="5">
+        <v>46275</v>
+      </c>
+      <c r="H43" s="2">
+        <v>13</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>8097</v>
+      </c>
+      <c r="B44" s="2">
+        <v>13708</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="2">
+        <v>39</v>
+      </c>
+      <c r="E44" s="2">
+        <v>41</v>
+      </c>
+      <c r="F44" s="4">
+        <v>2000</v>
+      </c>
+      <c r="G44" s="5">
+        <v>46275</v>
+      </c>
+      <c r="H44" s="2">
+        <v>13</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>8098</v>
+      </c>
+      <c r="B45" s="2">
+        <v>15534</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="2">
+        <v>39</v>
+      </c>
+      <c r="E45" s="2">
+        <v>41</v>
+      </c>
+      <c r="F45" s="4">
         <v>400</v>
       </c>
-      <c r="G37">
-        <v>46265</v>
-      </c>
-      <c r="H37">
+      <c r="G45" s="5">
+        <v>46275</v>
+      </c>
+      <c r="H45" s="2">
         <v>13</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I45" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>8013</v>
-      </c>
-      <c r="B38">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>8099</v>
+      </c>
+      <c r="B46" s="2">
+        <v>15533</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="2">
+        <v>39</v>
+      </c>
+      <c r="E46" s="2">
+        <v>41</v>
+      </c>
+      <c r="F46" s="4">
+        <v>200</v>
+      </c>
+      <c r="G46" s="5">
+        <v>46275</v>
+      </c>
+      <c r="H46" s="2">
+        <v>13</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>8104</v>
+      </c>
+      <c r="B47" s="2">
+        <v>16477</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" s="2">
+        <v>39</v>
+      </c>
+      <c r="E47" s="2">
+        <v>41</v>
+      </c>
+      <c r="F47" s="4">
+        <v>300</v>
+      </c>
+      <c r="G47" s="5">
+        <v>46273</v>
+      </c>
+      <c r="H47" s="2">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>8123</v>
+      </c>
+      <c r="B48" s="2">
+        <v>11847</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48" s="2">
+        <v>39</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4">
+        <v>400</v>
+      </c>
+      <c r="G48" s="5">
+        <v>46276</v>
+      </c>
+      <c r="H48" s="2">
+        <v>13</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>8126</v>
+      </c>
+      <c r="B49" s="2">
+        <v>30095</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D49" s="2">
+        <v>39</v>
+      </c>
+      <c r="E49" s="2">
+        <v>41</v>
+      </c>
+      <c r="F49" s="4">
+        <v>400</v>
+      </c>
+      <c r="G49" s="5">
+        <v>46276</v>
+      </c>
+      <c r="H49" s="2">
+        <v>13</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>8142</v>
+      </c>
+      <c r="B50" s="2">
+        <v>11845</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" s="2">
+        <v>39</v>
+      </c>
+      <c r="E50" s="2">
+        <v>41</v>
+      </c>
+      <c r="F50" s="4">
+        <v>1700</v>
+      </c>
+      <c r="G50" s="5">
+        <v>46276</v>
+      </c>
+      <c r="H50" s="2">
+        <v>13</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>8147</v>
+      </c>
+      <c r="B51" s="2">
         <v>15360</v>
       </c>
-      <c r="C38" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38">
-        <v>39</v>
-      </c>
-      <c r="E38">
-        <v>41</v>
-      </c>
-      <c r="F38">
-        <v>120</v>
-      </c>
-      <c r="G38">
-        <v>46262</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>8034</v>
-      </c>
-      <c r="B39">
-        <v>15727</v>
-      </c>
-      <c r="C39" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39">
-        <v>39</v>
-      </c>
-      <c r="E39">
-        <v>41</v>
-      </c>
-      <c r="F39">
-        <v>200</v>
-      </c>
-      <c r="G39">
-        <v>46265</v>
-      </c>
-      <c r="H39">
+      <c r="C51" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D51" s="2">
+        <v>39</v>
+      </c>
+      <c r="E51" s="2">
+        <v>41</v>
+      </c>
+      <c r="F51" s="4">
+        <v>100</v>
+      </c>
+      <c r="G51" s="5">
+        <v>46274</v>
+      </c>
+      <c r="H51" s="2">
         <v>2</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I51" s="3" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>8035</v>
-      </c>
-      <c r="B40">
-        <v>15534</v>
-      </c>
-      <c r="C40" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40">
-        <v>39</v>
-      </c>
-      <c r="E40">
-        <v>41</v>
-      </c>
-      <c r="F40">
-        <v>400</v>
-      </c>
-      <c r="G40">
-        <v>46265</v>
-      </c>
-      <c r="H40">
-        <v>13</v>
-      </c>
-      <c r="I40" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>8043</v>
-      </c>
-      <c r="B41">
-        <v>17322</v>
-      </c>
-      <c r="C41" t="s">
-        <v>53</v>
-      </c>
-      <c r="D41">
-        <v>39</v>
-      </c>
-      <c r="E41">
-        <v>41</v>
-      </c>
-      <c r="F41">
-        <v>400</v>
-      </c>
-      <c r="G41">
-        <v>46265</v>
-      </c>
-      <c r="H41">
-        <v>2</v>
-      </c>
-      <c r="I41" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>8046</v>
-      </c>
-      <c r="B42">
-        <v>17883</v>
-      </c>
-      <c r="C42" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42">
-        <v>39</v>
-      </c>
-      <c r="E42">
-        <v>41</v>
-      </c>
-      <c r="F42">
-        <v>200</v>
-      </c>
-      <c r="G42">
-        <v>46266</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>8047</v>
-      </c>
-      <c r="B43">
-        <v>17884</v>
-      </c>
-      <c r="C43" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43">
-        <v>39</v>
-      </c>
-      <c r="E43">
-        <v>41</v>
-      </c>
-      <c r="F43">
-        <v>200</v>
-      </c>
-      <c r="G43">
-        <v>46266</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>8048</v>
-      </c>
-      <c r="B44">
-        <v>17882</v>
-      </c>
-      <c r="C44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D44">
-        <v>39</v>
-      </c>
-      <c r="E44">
-        <v>41</v>
-      </c>
-      <c r="F44">
-        <v>200</v>
-      </c>
-      <c r="G44">
-        <v>46266</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>8049</v>
-      </c>
-      <c r="B45">
-        <v>17881</v>
-      </c>
-      <c r="C45" t="s">
-        <v>57</v>
-      </c>
-      <c r="D45">
-        <v>39</v>
-      </c>
-      <c r="E45">
-        <v>41</v>
-      </c>
-      <c r="F45">
-        <v>200</v>
-      </c>
-      <c r="G45">
-        <v>46266</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>8050</v>
-      </c>
-      <c r="B46">
-        <v>17878</v>
-      </c>
-      <c r="C46" t="s">
-        <v>58</v>
-      </c>
-      <c r="D46">
-        <v>39</v>
-      </c>
-      <c r="E46">
-        <v>41</v>
-      </c>
-      <c r="F46">
-        <v>200</v>
-      </c>
-      <c r="G46">
-        <v>46266</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>8051</v>
-      </c>
-      <c r="B47">
-        <v>15651</v>
-      </c>
-      <c r="C47" t="s">
-        <v>59</v>
-      </c>
-      <c r="D47">
-        <v>39</v>
-      </c>
-      <c r="E47">
-        <v>41</v>
-      </c>
-      <c r="F47">
-        <v>200</v>
-      </c>
-      <c r="G47">
-        <v>46274</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>8054</v>
-      </c>
-      <c r="B48">
-        <v>17890</v>
-      </c>
-      <c r="C48" t="s">
-        <v>60</v>
-      </c>
-      <c r="D48">
-        <v>39</v>
-      </c>
-      <c r="E48">
-        <v>41</v>
-      </c>
-      <c r="F48">
-        <v>200</v>
-      </c>
-      <c r="G48">
-        <v>46266</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>8071</v>
-      </c>
-      <c r="B49">
-        <v>17323</v>
-      </c>
-      <c r="C49" t="s">
-        <v>61</v>
-      </c>
-      <c r="D49">
-        <v>39</v>
-      </c>
-      <c r="E49">
-        <v>41</v>
-      </c>
-      <c r="F49">
-        <v>400</v>
-      </c>
-      <c r="G49">
-        <v>46268</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/ordens.xlsx
+++ b/data-source/ordens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/prompt-smart-stock-sight (4) (1)antig/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_A83E0076CB385EDFDA183BCB61CCBEC488860D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{878B015C-473E-4BC0-936B-8B971B83D889}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_A83E0076CB385EDFDA183BCB61CCBEC488860D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E777957E-FA5D-4831-9044-C986282FA064}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
   <si>
     <t>Nro.OP</t>
   </si>
@@ -88,9 +88,6 @@
     <t>DENVER NUDE</t>
   </si>
   <si>
-    <t>CANYON CASTOR</t>
-  </si>
-  <si>
     <t>CANYON BEGE</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
     <t>CORDOBA BEGE</t>
   </si>
   <si>
-    <t>BERGAMO NATURAL</t>
-  </si>
-  <si>
     <t>DENVER PRETO</t>
   </si>
   <si>
@@ -154,39 +148,12 @@
     <t>SORRENTO OFF WHITE</t>
   </si>
   <si>
-    <t>LENNY MANTEIGA</t>
-  </si>
-  <si>
     <t>MIRAGE OURO LIGHT</t>
   </si>
   <si>
     <t>MACKAY GLAM OURO LIGHT</t>
   </si>
   <si>
-    <t>ASPEN PRATA</t>
-  </si>
-  <si>
-    <t>ASPEN OURO LIGHT</t>
-  </si>
-  <si>
-    <t>ASPEN GRAFITE</t>
-  </si>
-  <si>
-    <t>ASPEN BRONZE</t>
-  </si>
-  <si>
-    <t>ASPEN WHISKY</t>
-  </si>
-  <si>
-    <t>SALERNO LIMONCELLO</t>
-  </si>
-  <si>
-    <t>ASPEN BROWN</t>
-  </si>
-  <si>
-    <t>MACKAY GLAM GRAFITE</t>
-  </si>
-  <si>
     <t>BORGONHA BROWN</t>
   </si>
   <si>
@@ -199,13 +166,37 @@
     <t>DENVER CANELA</t>
   </si>
   <si>
-    <t>MIRAGE PRATA</t>
-  </si>
-  <si>
     <t>BORGONHA GRAFITE</t>
   </si>
   <si>
     <t>BORGONHA WHISKY</t>
+  </si>
+  <si>
+    <t>MIRAGE OURO ROSADO</t>
+  </si>
+  <si>
+    <t>TRANSFE</t>
+  </si>
+  <si>
+    <t>LENNY PRETO</t>
+  </si>
+  <si>
+    <t>NAPA LINHO DAKAR NATURAL</t>
+  </si>
+  <si>
+    <t>NAPA LINHO DAKAR CARAMELO</t>
+  </si>
+  <si>
+    <t>TEGUS BEGE</t>
+  </si>
+  <si>
+    <t>TEGUS CANELA</t>
+  </si>
+  <si>
+    <t>TEGUS OFF WHITE</t>
+  </si>
+  <si>
+    <t>TEGUS PRETO</t>
   </si>
 </sst>
 </file>
@@ -718,25 +709,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>6911</v>
+        <v>6876</v>
       </c>
       <c r="B4" s="2">
-        <v>14180</v>
+        <v>15535</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2">
         <v>39</v>
       </c>
       <c r="E4" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="4">
-        <v>132</v>
+        <v>125.5</v>
       </c>
       <c r="G4" s="5">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="H4" s="2">
         <v>10</v>
@@ -747,13 +738,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>6937</v>
+        <v>6911</v>
       </c>
       <c r="B5" s="2">
-        <v>12879</v>
+        <v>14180</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2">
         <v>39</v>
@@ -762,27 +753,27 @@
         <v>40</v>
       </c>
       <c r="F5" s="4">
-        <v>240</v>
+        <v>132</v>
       </c>
       <c r="G5" s="5">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="H5" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>6938</v>
+        <v>6937</v>
       </c>
       <c r="B6" s="2">
-        <v>12883</v>
+        <v>12879</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2">
         <v>39</v>
@@ -805,13 +796,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>6939</v>
+        <v>6938</v>
       </c>
       <c r="B7" s="2">
-        <v>12776</v>
+        <v>12883</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2">
         <v>39</v>
@@ -834,13 +825,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>6940</v>
+        <v>6939</v>
       </c>
       <c r="B8" s="2">
-        <v>12878</v>
+        <v>12776</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="2">
         <v>39</v>
@@ -863,25 +854,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>7025</v>
+        <v>6940</v>
       </c>
       <c r="B9" s="2">
-        <v>17416</v>
+        <v>12878</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2">
         <v>39</v>
       </c>
       <c r="E9" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="4">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G9" s="5">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -892,13 +883,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>7425</v>
+        <v>7428</v>
       </c>
       <c r="B10" s="2">
-        <v>16633</v>
+        <v>16475</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2">
         <v>39</v>
@@ -907,27 +898,27 @@
         <v>41</v>
       </c>
       <c r="F10" s="4">
-        <v>187.5</v>
+        <v>400</v>
       </c>
       <c r="G10" s="5">
         <v>46230</v>
       </c>
       <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>7427</v>
+        <v>7489</v>
       </c>
       <c r="B11" s="2">
-        <v>16477</v>
+        <v>9000183</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="2">
         <v>39</v>
@@ -936,27 +927,27 @@
         <v>41</v>
       </c>
       <c r="F11" s="4">
-        <v>600</v>
+        <v>84</v>
       </c>
       <c r="G11" s="5">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="H11" s="2">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>7428</v>
+        <v>7623</v>
       </c>
       <c r="B12" s="2">
-        <v>16475</v>
+        <v>12398</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D12" s="2">
         <v>39</v>
@@ -965,27 +956,27 @@
         <v>41</v>
       </c>
       <c r="F12" s="4">
-        <v>400</v>
+        <v>115</v>
       </c>
       <c r="G12" s="5">
-        <v>46230</v>
+        <v>46240</v>
       </c>
       <c r="H12" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>7489</v>
+        <v>7624</v>
       </c>
       <c r="B13" s="2">
-        <v>9000183</v>
+        <v>12399</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2">
         <v>39</v>
@@ -994,27 +985,27 @@
         <v>41</v>
       </c>
       <c r="F13" s="4">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="G13" s="5">
-        <v>46223</v>
+        <v>46240</v>
       </c>
       <c r="H13" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>7623</v>
+        <v>7912</v>
       </c>
       <c r="B14" s="2">
-        <v>12398</v>
+        <v>11844</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="2">
         <v>39</v>
@@ -1023,27 +1014,27 @@
         <v>41</v>
       </c>
       <c r="F14" s="4">
-        <v>115</v>
+        <v>1000</v>
       </c>
       <c r="G14" s="5">
-        <v>46240</v>
+        <v>46260</v>
       </c>
       <c r="H14" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>7624</v>
+        <v>7913</v>
       </c>
       <c r="B15" s="2">
-        <v>12399</v>
+        <v>12400</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D15" s="2">
         <v>39</v>
@@ -1052,85 +1043,85 @@
         <v>41</v>
       </c>
       <c r="F15" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G15" s="5">
-        <v>46240</v>
+        <v>46260</v>
       </c>
       <c r="H15" s="2">
         <v>13</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>7912</v>
+        <v>7934</v>
       </c>
       <c r="B16" s="2">
-        <v>11844</v>
+        <v>13167</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D16" s="2">
         <v>39</v>
       </c>
       <c r="E16" s="2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F16" s="4">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="G16" s="5">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="H16" s="2">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>7913</v>
+        <v>7999</v>
       </c>
       <c r="B17" s="2">
-        <v>12400</v>
+        <v>17425</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="2">
+        <v>39</v>
+      </c>
+      <c r="E17" s="2">
+        <v>41</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="5">
+        <v>46265</v>
+      </c>
+      <c r="H17" s="2">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="D17" s="2">
-        <v>39</v>
-      </c>
-      <c r="E17" s="2">
-        <v>41</v>
-      </c>
-      <c r="F17" s="4">
-        <v>150</v>
-      </c>
-      <c r="G17" s="5">
-        <v>46260</v>
-      </c>
-      <c r="H17" s="2">
-        <v>13</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>7934</v>
+        <v>8000</v>
       </c>
       <c r="B18" s="2">
-        <v>13167</v>
+        <v>17416</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D18" s="2">
         <v>39</v>
@@ -1139,24 +1130,24 @@
         <v>41</v>
       </c>
       <c r="F18" s="4">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G18" s="5">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="H18" s="2">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>7996</v>
+        <v>8001</v>
       </c>
       <c r="B19" s="2">
-        <v>6411</v>
+        <v>15686</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>37</v>
@@ -1174,21 +1165,21 @@
         <v>46265</v>
       </c>
       <c r="H19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>7997</v>
+        <v>8002</v>
       </c>
       <c r="B20" s="2">
-        <v>11845</v>
+        <v>13708</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D20" s="2">
         <v>39</v>
@@ -1203,21 +1194,21 @@
         <v>46265</v>
       </c>
       <c r="H20" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>7998</v>
+        <v>8003</v>
       </c>
       <c r="B21" s="2">
-        <v>17420</v>
+        <v>16605</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D21" s="2">
         <v>39</v>
@@ -1226,27 +1217,27 @@
         <v>41</v>
       </c>
       <c r="F21" s="4">
-        <v>1000</v>
+        <v>624.5</v>
       </c>
       <c r="G21" s="5">
         <v>46265</v>
       </c>
       <c r="H21" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>7999</v>
+        <v>8043</v>
       </c>
       <c r="B22" s="2">
-        <v>17425</v>
+        <v>17322</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D22" s="2">
         <v>39</v>
@@ -1255,27 +1246,27 @@
         <v>41</v>
       </c>
       <c r="F22" s="4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="G22" s="5">
         <v>46265</v>
       </c>
       <c r="H22" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>8000</v>
+        <v>8091</v>
       </c>
       <c r="B23" s="2">
-        <v>17416</v>
+        <v>11845</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D23" s="2">
         <v>39</v>
@@ -1284,27 +1275,27 @@
         <v>41</v>
       </c>
       <c r="F23" s="4">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="G23" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H23" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>8001</v>
+        <v>8092</v>
       </c>
       <c r="B24" s="2">
-        <v>15686</v>
+        <v>30096</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D24" s="2">
         <v>39</v>
@@ -1313,27 +1304,27 @@
         <v>41</v>
       </c>
       <c r="F24" s="4">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="G24" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>8002</v>
+        <v>8093</v>
       </c>
       <c r="B25" s="2">
-        <v>13708</v>
+        <v>15212</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D25" s="2">
         <v>39</v>
@@ -1342,27 +1333,27 @@
         <v>41</v>
       </c>
       <c r="F25" s="4">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="G25" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H25" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>8003</v>
+        <v>8095</v>
       </c>
       <c r="B26" s="2">
-        <v>16605</v>
+        <v>17231</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D26" s="2">
         <v>39</v>
@@ -1374,24 +1365,24 @@
         <v>1000</v>
       </c>
       <c r="G26" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>8004</v>
+        <v>8096</v>
       </c>
       <c r="B27" s="2">
-        <v>11779</v>
+        <v>17256</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D27" s="2">
         <v>39</v>
@@ -1400,10 +1391,10 @@
         <v>41</v>
       </c>
       <c r="F27" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G27" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H27" s="2">
         <v>2</v>
@@ -1414,13 +1405,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>8035</v>
+        <v>8097</v>
       </c>
       <c r="B28" s="2">
-        <v>15534</v>
+        <v>13708</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D28" s="2">
         <v>39</v>
@@ -1429,27 +1420,27 @@
         <v>41</v>
       </c>
       <c r="F28" s="4">
-        <v>270.5</v>
+        <v>2000</v>
       </c>
       <c r="G28" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H28" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>8043</v>
+        <v>8098</v>
       </c>
       <c r="B29" s="2">
-        <v>17322</v>
+        <v>15534</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D29" s="2">
         <v>39</v>
@@ -1458,27 +1449,27 @@
         <v>41</v>
       </c>
       <c r="F29" s="4">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G29" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H29" s="2">
+        <v>2</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>8046</v>
+        <v>8104</v>
       </c>
       <c r="B30" s="2">
-        <v>17883</v>
+        <v>16477</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D30" s="2">
         <v>39</v>
@@ -1487,24 +1478,24 @@
         <v>41</v>
       </c>
       <c r="F30" s="4">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G30" s="5">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="H30" s="2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>8047</v>
+        <v>8123</v>
       </c>
       <c r="B31" s="2">
-        <v>17884</v>
+        <v>11847</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>47</v>
@@ -1516,24 +1507,24 @@
         <v>41</v>
       </c>
       <c r="F31" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G31" s="5">
-        <v>46266</v>
+        <v>46276</v>
       </c>
       <c r="H31" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>8048</v>
+        <v>8126</v>
       </c>
       <c r="B32" s="2">
-        <v>17882</v>
+        <v>30095</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>48</v>
@@ -1545,27 +1536,27 @@
         <v>41</v>
       </c>
       <c r="F32" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G32" s="5">
-        <v>46266</v>
+        <v>46276</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>8049</v>
+        <v>8142</v>
       </c>
       <c r="B33" s="2">
-        <v>17881</v>
+        <v>11845</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="D33" s="2">
         <v>39</v>
@@ -1574,27 +1565,27 @@
         <v>41</v>
       </c>
       <c r="F33" s="4">
-        <v>200</v>
+        <v>1700</v>
       </c>
       <c r="G33" s="5">
-        <v>46266</v>
+        <v>46276</v>
       </c>
       <c r="H33" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>8050</v>
+        <v>8184</v>
       </c>
       <c r="B34" s="2">
-        <v>17878</v>
+        <v>6395</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D34" s="2">
         <v>39</v>
@@ -1603,24 +1594,24 @@
         <v>41</v>
       </c>
       <c r="F34" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G34" s="5">
-        <v>46266</v>
+        <v>46282</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>8051</v>
+        <v>8185</v>
       </c>
       <c r="B35" s="2">
-        <v>15651</v>
+        <v>15363</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>51</v>
@@ -1632,10 +1623,10 @@
         <v>41</v>
       </c>
       <c r="F35" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G35" s="5">
-        <v>46274</v>
+        <v>46282</v>
       </c>
       <c r="H35" s="2">
         <v>6</v>
@@ -1646,13 +1637,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>8054</v>
+        <v>8186</v>
       </c>
       <c r="B36" s="2">
-        <v>17890</v>
+        <v>17420</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="D36" s="2">
         <v>39</v>
@@ -1661,27 +1652,27 @@
         <v>41</v>
       </c>
       <c r="F36" s="4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G36" s="5">
-        <v>46266</v>
+        <v>46282</v>
       </c>
       <c r="H36" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>8071</v>
+        <v>8187</v>
       </c>
       <c r="B37" s="2">
-        <v>17323</v>
+        <v>11779</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D37" s="2">
         <v>39</v>
@@ -1690,56 +1681,56 @@
         <v>41</v>
       </c>
       <c r="F37" s="4">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G37" s="5">
-        <v>46268</v>
+        <v>46283</v>
       </c>
       <c r="H37" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>8091</v>
+        <v>8189</v>
       </c>
       <c r="B38" s="2">
-        <v>11845</v>
+        <v>13144</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="2">
+        <v>39</v>
+      </c>
+      <c r="E38" s="2">
+        <v>41</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G38" s="5">
+        <v>46283</v>
+      </c>
+      <c r="H38" s="2">
+        <v>13</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="D38" s="2">
-        <v>39</v>
-      </c>
-      <c r="E38" s="2">
-        <v>41</v>
-      </c>
-      <c r="F38" s="4">
-        <v>300</v>
-      </c>
-      <c r="G38" s="5">
-        <v>46275</v>
-      </c>
-      <c r="H38" s="2">
-        <v>0</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>8092</v>
+        <v>8230</v>
       </c>
       <c r="B39" s="2">
-        <v>30096</v>
+        <v>14558</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D39" s="2">
         <v>39</v>
@@ -1748,27 +1739,27 @@
         <v>41</v>
       </c>
       <c r="F39" s="4">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G39" s="5">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="H39" s="2">
         <v>13</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>8093</v>
+        <v>8234</v>
       </c>
       <c r="B40" s="2">
-        <v>15212</v>
+        <v>15711</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D40" s="2">
         <v>39</v>
@@ -1777,27 +1768,27 @@
         <v>41</v>
       </c>
       <c r="F40" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G40" s="5">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="H40" s="2">
         <v>13</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>8094</v>
+        <v>8235</v>
       </c>
       <c r="B41" s="2">
-        <v>6395</v>
+        <v>15709</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2">
         <v>39</v>
@@ -1806,27 +1797,27 @@
         <v>41</v>
       </c>
       <c r="F41" s="4">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G41" s="5">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="H41" s="2">
         <v>13</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>8095</v>
+        <v>8236</v>
       </c>
       <c r="B42" s="2">
-        <v>17231</v>
+        <v>15713</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D42" s="2">
         <v>39</v>
@@ -1835,24 +1826,24 @@
         <v>41</v>
       </c>
       <c r="F42" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G42" s="5">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="H42" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>8096</v>
+        <v>8237</v>
       </c>
       <c r="B43" s="2">
-        <v>17256</v>
+        <v>15714</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>57</v>
@@ -1864,27 +1855,27 @@
         <v>41</v>
       </c>
       <c r="F43" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G43" s="5">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="H43" s="2">
         <v>13</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>8097</v>
+        <v>8255</v>
       </c>
       <c r="B44" s="2">
-        <v>13708</v>
+        <v>15212</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D44" s="2">
         <v>39</v>
@@ -1893,220 +1884,94 @@
         <v>41</v>
       </c>
       <c r="F44" s="4">
-        <v>2000</v>
+        <v>390</v>
       </c>
       <c r="G44" s="5">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="H44" s="2">
         <v>13</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
-        <v>8098</v>
-      </c>
-      <c r="B45" s="2">
-        <v>15534</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" s="2">
-        <v>39</v>
-      </c>
-      <c r="E45" s="2">
-        <v>41</v>
-      </c>
-      <c r="F45" s="4">
-        <v>400</v>
-      </c>
-      <c r="G45" s="5">
-        <v>46275</v>
-      </c>
-      <c r="H45" s="2">
-        <v>13</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="3"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
-        <v>8099</v>
-      </c>
-      <c r="B46" s="2">
-        <v>15533</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D46" s="2">
-        <v>39</v>
-      </c>
-      <c r="E46" s="2">
-        <v>41</v>
-      </c>
-      <c r="F46" s="4">
-        <v>200</v>
-      </c>
-      <c r="G46" s="5">
-        <v>46275</v>
-      </c>
-      <c r="H46" s="2">
-        <v>13</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="3"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
-        <v>8104</v>
-      </c>
-      <c r="B47" s="2">
-        <v>16477</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" s="2">
-        <v>39</v>
-      </c>
-      <c r="E47" s="2">
-        <v>41</v>
-      </c>
-      <c r="F47" s="4">
-        <v>300</v>
-      </c>
-      <c r="G47" s="5">
-        <v>46273</v>
-      </c>
-      <c r="H47" s="2">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="3"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
-        <v>8123</v>
-      </c>
-      <c r="B48" s="2">
-        <v>11847</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" s="2">
-        <v>39</v>
-      </c>
-      <c r="E48" s="2">
-        <v>0</v>
-      </c>
-      <c r="F48" s="4">
-        <v>400</v>
-      </c>
-      <c r="G48" s="5">
-        <v>46276</v>
-      </c>
-      <c r="H48" s="2">
-        <v>13</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="3"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
-        <v>8126</v>
-      </c>
-      <c r="B49" s="2">
-        <v>30095</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49" s="2">
-        <v>39</v>
-      </c>
-      <c r="E49" s="2">
-        <v>41</v>
-      </c>
-      <c r="F49" s="4">
-        <v>400</v>
-      </c>
-      <c r="G49" s="5">
-        <v>46276</v>
-      </c>
-      <c r="H49" s="2">
-        <v>13</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="3"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
-        <v>8142</v>
-      </c>
-      <c r="B50" s="2">
-        <v>11845</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D50" s="2">
-        <v>39</v>
-      </c>
-      <c r="E50" s="2">
-        <v>41</v>
-      </c>
-      <c r="F50" s="4">
-        <v>1700</v>
-      </c>
-      <c r="G50" s="5">
-        <v>46276</v>
-      </c>
-      <c r="H50" s="2">
-        <v>13</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="3"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
-        <v>8147</v>
-      </c>
-      <c r="B51" s="2">
-        <v>15360</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D51" s="2">
-        <v>39</v>
-      </c>
-      <c r="E51" s="2">
-        <v>41</v>
-      </c>
-      <c r="F51" s="4">
-        <v>100</v>
-      </c>
-      <c r="G51" s="5">
-        <v>46274</v>
-      </c>
-      <c r="H51" s="2">
-        <v>2</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="3"/>
     </row>
   </sheetData>
   <printOptions gridLines="1"/>

--- a/data-source/ordens.xlsx
+++ b/data-source/ordens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/prompt-smart-stock-sight (4) (1)antig/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_A83E0076CB385EDFDA183BCB61CCBEC488860D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E777957E-FA5D-4831-9044-C986282FA064}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_A83E0076CB385EDFDA183BCB61CCBEC488860D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{370DA4A7-F677-4791-BC45-46094C0CB238}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="56">
   <si>
     <t>Nro.OP</t>
   </si>
@@ -85,18 +85,12 @@
     <t>KALAHARI PRETO</t>
   </si>
   <si>
-    <t>DENVER NUDE</t>
-  </si>
-  <si>
     <t>CANYON BEGE</t>
   </si>
   <si>
     <t>RAMA</t>
   </si>
   <si>
-    <t>NAPA MADRID CONHAQUE</t>
-  </si>
-  <si>
     <t>DENVER ESPRESSO</t>
   </si>
   <si>
@@ -127,15 +121,9 @@
     <t>LILLY OFF WHITE</t>
   </si>
   <si>
-    <t>GR 1</t>
-  </si>
-  <si>
     <t>CORDOBA BEGE</t>
   </si>
   <si>
-    <t>DENVER PRETO</t>
-  </si>
-  <si>
     <t>LILLY ROSE</t>
   </si>
   <si>
@@ -151,9 +139,6 @@
     <t>MIRAGE OURO LIGHT</t>
   </si>
   <si>
-    <t>MACKAY GLAM OURO LIGHT</t>
-  </si>
-  <si>
     <t>BORGONHA BROWN</t>
   </si>
   <si>
@@ -169,34 +154,43 @@
     <t>BORGONHA GRAFITE</t>
   </si>
   <si>
-    <t>BORGONHA WHISKY</t>
-  </si>
-  <si>
     <t>MIRAGE OURO ROSADO</t>
   </si>
   <si>
     <t>TRANSFE</t>
   </si>
   <si>
-    <t>LENNY PRETO</t>
-  </si>
-  <si>
     <t>NAPA LINHO DAKAR NATURAL</t>
   </si>
   <si>
-    <t>NAPA LINHO DAKAR CARAMELO</t>
-  </si>
-  <si>
-    <t>TEGUS BEGE</t>
-  </si>
-  <si>
-    <t>TEGUS CANELA</t>
-  </si>
-  <si>
-    <t>TEGUS OFF WHITE</t>
-  </si>
-  <si>
-    <t>TEGUS PRETO</t>
+    <t>BERGAMO OFF WHITE</t>
+  </si>
+  <si>
+    <t>NAPA BARI FOSCO PRETO</t>
+  </si>
+  <si>
+    <t>NAPA BARI FOSCO BEGE</t>
+  </si>
+  <si>
+    <t>SALERNO CARAMELO</t>
+  </si>
+  <si>
+    <t>GLOMER NATURAL</t>
+  </si>
+  <si>
+    <t>ARUBA GLAM OURO LIGHT</t>
+  </si>
+  <si>
+    <t>ARUBA GLAM PRETO</t>
+  </si>
+  <si>
+    <t>ARUBA OFF WHITE</t>
+  </si>
+  <si>
+    <t>ARUBA GLAM PRATA</t>
+  </si>
+  <si>
+    <t>ARUBA GLAM OURO ROSADO</t>
   </si>
 </sst>
 </file>
@@ -715,7 +709,7 @@
         <v>15535</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D4" s="2">
         <v>39</v>
@@ -724,7 +718,7 @@
         <v>41</v>
       </c>
       <c r="F4" s="4">
-        <v>125.5</v>
+        <v>57.5</v>
       </c>
       <c r="G4" s="5">
         <v>46190</v>
@@ -889,7 +883,7 @@
         <v>16475</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2">
         <v>39</v>
@@ -912,13 +906,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>7489</v>
+        <v>7623</v>
       </c>
       <c r="B11" s="2">
-        <v>9000183</v>
+        <v>12398</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2">
         <v>39</v>
@@ -927,27 +921,27 @@
         <v>41</v>
       </c>
       <c r="F11" s="4">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G11" s="5">
-        <v>46223</v>
+        <v>46240</v>
       </c>
       <c r="H11" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>7623</v>
+        <v>7624</v>
       </c>
       <c r="B12" s="2">
-        <v>12398</v>
+        <v>12399</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2">
         <v>39</v>
@@ -956,7 +950,7 @@
         <v>41</v>
       </c>
       <c r="F12" s="4">
-        <v>115</v>
+        <v>118.5</v>
       </c>
       <c r="G12" s="5">
         <v>46240</v>
@@ -970,13 +964,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>7624</v>
+        <v>7913</v>
       </c>
       <c r="B13" s="2">
-        <v>12399</v>
+        <v>12400</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2">
         <v>39</v>
@@ -985,27 +979,27 @@
         <v>41</v>
       </c>
       <c r="F13" s="4">
-        <v>200</v>
+        <v>98.5</v>
       </c>
       <c r="G13" s="5">
-        <v>46240</v>
+        <v>46260</v>
       </c>
       <c r="H13" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>7912</v>
+        <v>7934</v>
       </c>
       <c r="B14" s="2">
-        <v>11844</v>
+        <v>13167</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D14" s="2">
         <v>39</v>
@@ -1014,24 +1008,24 @@
         <v>41</v>
       </c>
       <c r="F14" s="4">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="G14" s="5">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="H14" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>7913</v>
+        <v>8001</v>
       </c>
       <c r="B15" s="2">
-        <v>12400</v>
+        <v>15686</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>33</v>
@@ -1043,27 +1037,27 @@
         <v>41</v>
       </c>
       <c r="F15" s="4">
-        <v>150</v>
+        <v>94.5</v>
       </c>
       <c r="G15" s="5">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="H15" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>7934</v>
+        <v>8002</v>
       </c>
       <c r="B16" s="2">
-        <v>13167</v>
+        <v>13708</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="2">
         <v>39</v>
@@ -1072,27 +1066,27 @@
         <v>41</v>
       </c>
       <c r="F16" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G16" s="5">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="H16" s="2">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>7999</v>
+        <v>8092</v>
       </c>
       <c r="B17" s="2">
-        <v>17425</v>
+        <v>30096</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D17" s="2">
         <v>39</v>
@@ -1101,27 +1095,27 @@
         <v>41</v>
       </c>
       <c r="F17" s="4">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="G17" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H17" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>8000</v>
+        <v>8093</v>
       </c>
       <c r="B18" s="2">
-        <v>17416</v>
+        <v>15212</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D18" s="2">
         <v>39</v>
@@ -1130,27 +1124,27 @@
         <v>41</v>
       </c>
       <c r="F18" s="4">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G18" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H18" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>8001</v>
+        <v>8095</v>
       </c>
       <c r="B19" s="2">
-        <v>15686</v>
+        <v>17231</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D19" s="2">
         <v>39</v>
@@ -1159,27 +1153,27 @@
         <v>41</v>
       </c>
       <c r="F19" s="4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G19" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>8002</v>
+        <v>8096</v>
       </c>
       <c r="B20" s="2">
-        <v>13708</v>
+        <v>17256</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D20" s="2">
         <v>39</v>
@@ -1191,24 +1185,24 @@
         <v>1000</v>
       </c>
       <c r="G20" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H20" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>8003</v>
+        <v>8097</v>
       </c>
       <c r="B21" s="2">
-        <v>16605</v>
+        <v>13708</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D21" s="2">
         <v>39</v>
@@ -1217,27 +1211,27 @@
         <v>41</v>
       </c>
       <c r="F21" s="4">
-        <v>624.5</v>
+        <v>2000</v>
       </c>
       <c r="G21" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H21" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>8043</v>
+        <v>8098</v>
       </c>
       <c r="B22" s="2">
-        <v>17322</v>
+        <v>15534</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D22" s="2">
         <v>39</v>
@@ -1246,56 +1240,56 @@
         <v>41</v>
       </c>
       <c r="F22" s="4">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="G22" s="5">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="H22" s="2">
+        <v>2</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>8091</v>
+        <v>8123</v>
       </c>
       <c r="B23" s="2">
-        <v>11845</v>
+        <v>11847</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="2">
+        <v>39</v>
+      </c>
+      <c r="E23" s="2">
+        <v>41</v>
+      </c>
+      <c r="F23" s="4">
+        <v>400</v>
+      </c>
+      <c r="G23" s="5">
+        <v>46276</v>
+      </c>
+      <c r="H23" s="2">
         <v>25</v>
       </c>
-      <c r="D23" s="2">
-        <v>39</v>
-      </c>
-      <c r="E23" s="2">
-        <v>41</v>
-      </c>
-      <c r="F23" s="4">
-        <v>300</v>
-      </c>
-      <c r="G23" s="5">
-        <v>46275</v>
-      </c>
-      <c r="H23" s="2">
-        <v>2</v>
-      </c>
       <c r="I23" s="3" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>8092</v>
+        <v>8184</v>
       </c>
       <c r="B24" s="2">
-        <v>30096</v>
+        <v>6395</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2">
         <v>39</v>
@@ -1304,27 +1298,27 @@
         <v>41</v>
       </c>
       <c r="F24" s="4">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G24" s="5">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="H24" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>8093</v>
+        <v>8186</v>
       </c>
       <c r="B25" s="2">
-        <v>15212</v>
+        <v>17420</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D25" s="2">
         <v>39</v>
@@ -1333,56 +1327,56 @@
         <v>41</v>
       </c>
       <c r="F25" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="5">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="H25" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>8095</v>
+        <v>8187</v>
       </c>
       <c r="B26" s="2">
-        <v>17231</v>
+        <v>11779</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="2">
+        <v>39</v>
+      </c>
+      <c r="E26" s="2">
+        <v>41</v>
+      </c>
+      <c r="F26" s="4">
+        <v>600</v>
+      </c>
+      <c r="G26" s="5">
+        <v>46283</v>
+      </c>
+      <c r="H26" s="2">
+        <v>13</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="D26" s="2">
-        <v>39</v>
-      </c>
-      <c r="E26" s="2">
-        <v>41</v>
-      </c>
-      <c r="F26" s="4">
-        <v>1000</v>
-      </c>
-      <c r="G26" s="5">
-        <v>46275</v>
-      </c>
-      <c r="H26" s="2">
-        <v>2</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>8096</v>
+        <v>8189</v>
       </c>
       <c r="B27" s="2">
-        <v>17256</v>
+        <v>13144</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" s="2">
         <v>39</v>
@@ -1394,7 +1388,7 @@
         <v>1000</v>
       </c>
       <c r="G27" s="5">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="H27" s="2">
         <v>2</v>
@@ -1405,13 +1399,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>8097</v>
+        <v>8255</v>
       </c>
       <c r="B28" s="2">
-        <v>13708</v>
+        <v>15212</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" s="2">
         <v>39</v>
@@ -1420,27 +1414,27 @@
         <v>41</v>
       </c>
       <c r="F28" s="4">
-        <v>2000</v>
+        <v>390</v>
       </c>
       <c r="G28" s="5">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="H28" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>8098</v>
+        <v>8291</v>
       </c>
       <c r="B29" s="2">
-        <v>15534</v>
+        <v>7148</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D29" s="2">
         <v>39</v>
@@ -1449,27 +1443,27 @@
         <v>41</v>
       </c>
       <c r="F29" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G29" s="5">
-        <v>46275</v>
+        <v>46287</v>
       </c>
       <c r="H29" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>8104</v>
+        <v>8292</v>
       </c>
       <c r="B30" s="2">
-        <v>16477</v>
+        <v>11845</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D30" s="2">
         <v>39</v>
@@ -1478,27 +1472,27 @@
         <v>41</v>
       </c>
       <c r="F30" s="4">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="G30" s="5">
-        <v>46273</v>
+        <v>46287</v>
       </c>
       <c r="H30" s="2">
         <v>13</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>8123</v>
+        <v>8293</v>
       </c>
       <c r="B31" s="2">
-        <v>11847</v>
+        <v>11844</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D31" s="2">
         <v>39</v>
@@ -1507,27 +1501,27 @@
         <v>41</v>
       </c>
       <c r="F31" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G31" s="5">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="H31" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>8126</v>
+        <v>8294</v>
       </c>
       <c r="B32" s="2">
-        <v>30095</v>
+        <v>16477</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D32" s="2">
         <v>39</v>
@@ -1539,24 +1533,24 @@
         <v>400</v>
       </c>
       <c r="G32" s="5">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="H32" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>8142</v>
+        <v>8295</v>
       </c>
       <c r="B33" s="2">
-        <v>11845</v>
+        <v>16642</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D33" s="2">
         <v>39</v>
@@ -1565,27 +1559,27 @@
         <v>41</v>
       </c>
       <c r="F33" s="4">
-        <v>1700</v>
+        <v>1000</v>
       </c>
       <c r="G33" s="5">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="H33" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>8184</v>
+        <v>8296</v>
       </c>
       <c r="B34" s="2">
-        <v>6395</v>
+        <v>16643</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D34" s="2">
         <v>39</v>
@@ -1594,27 +1588,27 @@
         <v>41</v>
       </c>
       <c r="F34" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G34" s="5">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="H34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>8185</v>
+        <v>8297</v>
       </c>
       <c r="B35" s="2">
-        <v>15363</v>
+        <v>16605</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D35" s="2">
         <v>39</v>
@@ -1623,27 +1617,27 @@
         <v>41</v>
       </c>
       <c r="F35" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G35" s="5">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="H35" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>8186</v>
+        <v>8298</v>
       </c>
       <c r="B36" s="2">
-        <v>17420</v>
+        <v>13144</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D36" s="2">
         <v>39</v>
@@ -1652,27 +1646,27 @@
         <v>41</v>
       </c>
       <c r="F36" s="4">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G36" s="5">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="H36" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>8187</v>
+        <v>8306</v>
       </c>
       <c r="B37" s="2">
-        <v>11779</v>
+        <v>14137</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D37" s="2">
         <v>39</v>
@@ -1681,27 +1675,27 @@
         <v>41</v>
       </c>
       <c r="F37" s="4">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="G37" s="5">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="H37" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>8189</v>
+        <v>8337</v>
       </c>
       <c r="B38" s="2">
-        <v>13144</v>
+        <v>13766</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D38" s="2">
         <v>39</v>
@@ -1710,27 +1704,27 @@
         <v>41</v>
       </c>
       <c r="F38" s="4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="G38" s="5">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="H38" s="2">
         <v>13</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>8230</v>
+        <v>8343</v>
       </c>
       <c r="B39" s="2">
-        <v>14558</v>
+        <v>17953</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D39" s="2">
         <v>39</v>
@@ -1739,27 +1733,27 @@
         <v>41</v>
       </c>
       <c r="F39" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G39" s="5">
-        <v>46281</v>
+        <v>46289</v>
       </c>
       <c r="H39" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>8234</v>
+        <v>8345</v>
       </c>
       <c r="B40" s="2">
-        <v>15711</v>
+        <v>17845</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D40" s="2">
         <v>39</v>
@@ -1771,24 +1765,24 @@
         <v>200</v>
       </c>
       <c r="G40" s="5">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="H40" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>8235</v>
+        <v>8352</v>
       </c>
       <c r="B41" s="2">
-        <v>15709</v>
+        <v>18009</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D41" s="2">
         <v>39</v>
@@ -1800,24 +1794,24 @@
         <v>200</v>
       </c>
       <c r="G41" s="5">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="H41" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>8236</v>
+        <v>8360</v>
       </c>
       <c r="B42" s="2">
-        <v>15713</v>
+        <v>17952</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D42" s="2">
         <v>39</v>
@@ -1829,24 +1823,24 @@
         <v>200</v>
       </c>
       <c r="G42" s="5">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="H42" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>8237</v>
+        <v>8361</v>
       </c>
       <c r="B43" s="2">
-        <v>15714</v>
+        <v>17954</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D43" s="2">
         <v>39</v>
@@ -1858,43 +1852,25 @@
         <v>200</v>
       </c>
       <c r="G43" s="5">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="H43" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
-        <v>8255</v>
-      </c>
-      <c r="B44" s="2">
-        <v>15212</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="2">
-        <v>39</v>
-      </c>
-      <c r="E44" s="2">
-        <v>41</v>
-      </c>
-      <c r="F44" s="4">
-        <v>390</v>
-      </c>
-      <c r="G44" s="5">
-        <v>46283</v>
-      </c>
-      <c r="H44" s="2">
-        <v>13</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="3"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>

--- a/data-source/ordens.xlsx
+++ b/data-source/ordens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/prompt-smart-stock-sight (4) (1)antig/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_A83E0076CB385EDFDA183BCB61CCBEC488860D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{370DA4A7-F677-4791-BC45-46094C0CB238}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_A83E0076CB385EDFDA183BCB61CCBEC488860D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB6E5F52-782B-4E20-817B-AA3C624C2388}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="50">
   <si>
     <t>Nro.OP</t>
   </si>
@@ -85,27 +85,15 @@
     <t>KALAHARI PRETO</t>
   </si>
   <si>
-    <t>CANYON BEGE</t>
-  </si>
-  <si>
     <t>RAMA</t>
   </si>
   <si>
-    <t>DENVER ESPRESSO</t>
-  </si>
-  <si>
     <t>BORGONHA OURO LIGHT</t>
   </si>
   <si>
     <t>JUMBO 1</t>
   </si>
   <si>
-    <t>LILLY PRETO</t>
-  </si>
-  <si>
-    <t>LILLY MANTEIGA</t>
-  </si>
-  <si>
     <t>BORGONHA PRATA</t>
   </si>
   <si>
@@ -118,79 +106,73 @@
     <t>RECOB</t>
   </si>
   <si>
-    <t>LILLY OFF WHITE</t>
-  </si>
-  <si>
     <t>CORDOBA BEGE</t>
   </si>
   <si>
     <t>LILLY ROSE</t>
   </si>
   <si>
-    <t>MERIDA PRETO</t>
-  </si>
-  <si>
-    <t>NAPA FLOATER VENEZIA DOURADO</t>
-  </si>
-  <si>
-    <t>SORRENTO OFF WHITE</t>
-  </si>
-  <si>
     <t>MIRAGE OURO LIGHT</t>
   </si>
   <si>
-    <t>BORGONHA BROWN</t>
-  </si>
-  <si>
-    <t>BORGONHA TITANIO</t>
-  </si>
-  <si>
-    <t>BORGONHA BRONZE</t>
-  </si>
-  <si>
     <t>DENVER CANELA</t>
   </si>
   <si>
-    <t>BORGONHA GRAFITE</t>
-  </si>
-  <si>
     <t>MIRAGE OURO ROSADO</t>
   </si>
   <si>
-    <t>TRANSFE</t>
-  </si>
-  <si>
-    <t>NAPA LINHO DAKAR NATURAL</t>
-  </si>
-  <si>
-    <t>BERGAMO OFF WHITE</t>
-  </si>
-  <si>
-    <t>NAPA BARI FOSCO PRETO</t>
-  </si>
-  <si>
-    <t>NAPA BARI FOSCO BEGE</t>
-  </si>
-  <si>
-    <t>SALERNO CARAMELO</t>
-  </si>
-  <si>
-    <t>GLOMER NATURAL</t>
-  </si>
-  <si>
     <t>ARUBA GLAM OURO LIGHT</t>
   </si>
   <si>
-    <t>ARUBA GLAM PRETO</t>
-  </si>
-  <si>
-    <t>ARUBA OFF WHITE</t>
-  </si>
-  <si>
     <t>ARUBA GLAM PRATA</t>
   </si>
   <si>
     <t>ARUBA GLAM OURO ROSADO</t>
+  </si>
+  <si>
+    <t>IMP DIG</t>
+  </si>
+  <si>
+    <t>ARUBA GLAM BRONZE</t>
+  </si>
+  <si>
+    <t>DELHI GLAM PRATA</t>
+  </si>
+  <si>
+    <t>DELHI GLAM OURO LIGHT</t>
+  </si>
+  <si>
+    <t>BORGONHA WHISKY</t>
+  </si>
+  <si>
+    <t>BORGONHA OURO ROSADO</t>
+  </si>
+  <si>
+    <t>CANYON CANELA</t>
+  </si>
+  <si>
+    <t>DENVER PRETO</t>
+  </si>
+  <si>
+    <t>DENVER NUDE</t>
+  </si>
+  <si>
+    <t>MIRAGE PRETO</t>
+  </si>
+  <si>
+    <t>SAVOY GLAM OURO LIGHT</t>
+  </si>
+  <si>
+    <t>SAVOY LUX BRANCO</t>
+  </si>
+  <si>
+    <t>TEGUS CANELA</t>
+  </si>
+  <si>
+    <t>DOHA OURO LIGHT</t>
+  </si>
+  <si>
+    <t>NAPA VIENA PVC OFF WHITE</t>
   </si>
 </sst>
 </file>
@@ -709,7 +691,7 @@
         <v>15535</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2">
         <v>39</v>
@@ -883,7 +865,7 @@
         <v>16475</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D10" s="2">
         <v>39</v>
@@ -906,13 +888,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>7623</v>
+        <v>7934</v>
       </c>
       <c r="B11" s="2">
-        <v>12398</v>
+        <v>13167</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" s="2">
         <v>39</v>
@@ -921,27 +903,27 @@
         <v>41</v>
       </c>
       <c r="F11" s="4">
-        <v>115</v>
+        <v>400</v>
       </c>
       <c r="G11" s="5">
-        <v>46240</v>
+        <v>46258</v>
       </c>
       <c r="H11" s="2">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>7624</v>
+        <v>8096</v>
       </c>
       <c r="B12" s="2">
-        <v>12399</v>
+        <v>17256</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2">
         <v>39</v>
@@ -950,27 +932,27 @@
         <v>41</v>
       </c>
       <c r="F12" s="4">
-        <v>118.5</v>
+        <v>1000</v>
       </c>
       <c r="G12" s="5">
-        <v>46240</v>
+        <v>46275</v>
       </c>
       <c r="H12" s="2">
+        <v>2</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>7913</v>
+        <v>8098</v>
       </c>
       <c r="B13" s="2">
-        <v>12400</v>
+        <v>15534</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D13" s="2">
         <v>39</v>
@@ -979,27 +961,27 @@
         <v>41</v>
       </c>
       <c r="F13" s="4">
-        <v>98.5</v>
+        <v>201.6</v>
       </c>
       <c r="G13" s="5">
-        <v>46260</v>
+        <v>46275</v>
       </c>
       <c r="H13" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>7934</v>
+        <v>8292</v>
       </c>
       <c r="B14" s="2">
-        <v>13167</v>
+        <v>11845</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D14" s="2">
         <v>39</v>
@@ -1008,27 +990,27 @@
         <v>41</v>
       </c>
       <c r="F14" s="4">
-        <v>400</v>
+        <v>12.5</v>
       </c>
       <c r="G14" s="5">
-        <v>46258</v>
+        <v>46287</v>
       </c>
       <c r="H14" s="2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>8001</v>
+        <v>8335</v>
       </c>
       <c r="B15" s="2">
-        <v>15686</v>
+        <v>11845</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D15" s="2">
         <v>39</v>
@@ -1037,27 +1019,27 @@
         <v>41</v>
       </c>
       <c r="F15" s="4">
-        <v>94.5</v>
+        <v>336</v>
       </c>
       <c r="G15" s="5">
-        <v>46265</v>
+        <v>46290</v>
       </c>
       <c r="H15" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>8002</v>
+        <v>8343</v>
       </c>
       <c r="B16" s="2">
-        <v>13708</v>
+        <v>17953</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2">
         <v>39</v>
@@ -1066,27 +1048,27 @@
         <v>41</v>
       </c>
       <c r="F16" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G16" s="5">
-        <v>46265</v>
+        <v>46289</v>
       </c>
       <c r="H16" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>8092</v>
+        <v>8360</v>
       </c>
       <c r="B17" s="2">
-        <v>30096</v>
+        <v>17952</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D17" s="2">
         <v>39</v>
@@ -1095,27 +1077,27 @@
         <v>41</v>
       </c>
       <c r="F17" s="4">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="G17" s="5">
-        <v>46275</v>
+        <v>46290</v>
       </c>
       <c r="H17" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>8093</v>
+        <v>8361</v>
       </c>
       <c r="B18" s="2">
-        <v>15212</v>
+        <v>17954</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D18" s="2">
         <v>39</v>
@@ -1124,27 +1106,27 @@
         <v>41</v>
       </c>
       <c r="F18" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G18" s="5">
-        <v>46275</v>
+        <v>46293</v>
       </c>
       <c r="H18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>8095</v>
+        <v>8362</v>
       </c>
       <c r="B19" s="2">
-        <v>17231</v>
+        <v>18000</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D19" s="2">
         <v>39</v>
@@ -1153,10 +1135,10 @@
         <v>41</v>
       </c>
       <c r="F19" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G19" s="5">
-        <v>46275</v>
+        <v>46293</v>
       </c>
       <c r="H19" s="2">
         <v>2</v>
@@ -1167,13 +1149,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>8096</v>
+        <v>8365</v>
       </c>
       <c r="B20" s="2">
-        <v>17256</v>
+        <v>18014</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D20" s="2">
         <v>39</v>
@@ -1182,27 +1164,27 @@
         <v>41</v>
       </c>
       <c r="F20" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G20" s="5">
-        <v>46275</v>
+        <v>46294</v>
       </c>
       <c r="H20" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>8097</v>
+        <v>8367</v>
       </c>
       <c r="B21" s="2">
-        <v>13708</v>
+        <v>18016</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D21" s="2">
         <v>39</v>
@@ -1211,27 +1193,27 @@
         <v>41</v>
       </c>
       <c r="F21" s="4">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="G21" s="5">
-        <v>46275</v>
+        <v>46294</v>
       </c>
       <c r="H21" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>8098</v>
+        <v>8378</v>
       </c>
       <c r="B22" s="2">
-        <v>15534</v>
+        <v>11844</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D22" s="2">
         <v>39</v>
@@ -1240,27 +1222,27 @@
         <v>41</v>
       </c>
       <c r="F22" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G22" s="5">
-        <v>46275</v>
+        <v>46295</v>
       </c>
       <c r="H22" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>8123</v>
+        <v>8379</v>
       </c>
       <c r="B23" s="2">
-        <v>11847</v>
+        <v>11845</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D23" s="2">
         <v>39</v>
@@ -1269,27 +1251,27 @@
         <v>41</v>
       </c>
       <c r="F23" s="4">
-        <v>400</v>
+        <v>1440</v>
       </c>
       <c r="G23" s="5">
-        <v>46276</v>
+        <v>46295</v>
       </c>
       <c r="H23" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>8184</v>
+        <v>8380</v>
       </c>
       <c r="B24" s="2">
-        <v>6395</v>
+        <v>30095</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" s="2">
         <v>39</v>
@@ -1301,24 +1283,24 @@
         <v>400</v>
       </c>
       <c r="G24" s="5">
-        <v>46282</v>
+        <v>46295</v>
       </c>
       <c r="H24" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>8186</v>
+        <v>8381</v>
       </c>
       <c r="B25" s="2">
-        <v>17420</v>
+        <v>11846</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D25" s="2">
         <v>39</v>
@@ -1327,27 +1309,27 @@
         <v>41</v>
       </c>
       <c r="F25" s="4">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="G25" s="5">
-        <v>46282</v>
+        <v>46295</v>
       </c>
       <c r="H25" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>8187</v>
+        <v>8382</v>
       </c>
       <c r="B26" s="2">
-        <v>11779</v>
+        <v>16503</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D26" s="2">
         <v>39</v>
@@ -1356,27 +1338,27 @@
         <v>41</v>
       </c>
       <c r="F26" s="4">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="G26" s="5">
-        <v>46283</v>
+        <v>46295</v>
       </c>
       <c r="H26" s="2">
         <v>13</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>8189</v>
+        <v>8383</v>
       </c>
       <c r="B27" s="2">
-        <v>13144</v>
+        <v>17425</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D27" s="2">
         <v>39</v>
@@ -1388,24 +1370,24 @@
         <v>1000</v>
       </c>
       <c r="G27" s="5">
-        <v>46283</v>
+        <v>46295</v>
       </c>
       <c r="H27" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>8255</v>
+        <v>8384</v>
       </c>
       <c r="B28" s="2">
-        <v>15212</v>
+        <v>17416</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D28" s="2">
         <v>39</v>
@@ -1414,27 +1396,27 @@
         <v>41</v>
       </c>
       <c r="F28" s="4">
-        <v>390</v>
+        <v>600</v>
       </c>
       <c r="G28" s="5">
-        <v>46283</v>
+        <v>46295</v>
       </c>
       <c r="H28" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>8291</v>
+        <v>8385</v>
       </c>
       <c r="B29" s="2">
-        <v>7148</v>
+        <v>17420</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D29" s="2">
         <v>39</v>
@@ -1443,27 +1425,27 @@
         <v>41</v>
       </c>
       <c r="F29" s="4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G29" s="5">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="H29" s="2">
         <v>13</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>8292</v>
+        <v>8386</v>
       </c>
       <c r="B30" s="2">
-        <v>11845</v>
+        <v>15536</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D30" s="2">
         <v>39</v>
@@ -1472,27 +1454,27 @@
         <v>41</v>
       </c>
       <c r="F30" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G30" s="5">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="H30" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>8293</v>
+        <v>8387</v>
       </c>
       <c r="B31" s="2">
-        <v>11844</v>
+        <v>16466</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D31" s="2">
         <v>39</v>
@@ -1501,27 +1483,27 @@
         <v>41</v>
       </c>
       <c r="F31" s="4">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="G31" s="5">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="H31" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>8294</v>
+        <v>8388</v>
       </c>
       <c r="B32" s="2">
-        <v>16477</v>
+        <v>16571</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D32" s="2">
         <v>39</v>
@@ -1530,24 +1512,24 @@
         <v>41</v>
       </c>
       <c r="F32" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G32" s="5">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="H32" s="2">
         <v>13</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>8295</v>
+        <v>8389</v>
       </c>
       <c r="B33" s="2">
-        <v>16642</v>
+        <v>15709</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>47</v>
@@ -1559,27 +1541,27 @@
         <v>41</v>
       </c>
       <c r="F33" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G33" s="5">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="H33" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>8296</v>
+        <v>8395</v>
       </c>
       <c r="B34" s="2">
-        <v>16643</v>
+        <v>11845</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D34" s="2">
         <v>39</v>
@@ -1588,27 +1570,27 @@
         <v>41</v>
       </c>
       <c r="F34" s="4">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="G34" s="5">
-        <v>46287</v>
+        <v>46297</v>
       </c>
       <c r="H34" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>8297</v>
+        <v>8423</v>
       </c>
       <c r="B35" s="2">
-        <v>16605</v>
+        <v>15686</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D35" s="2">
         <v>39</v>
@@ -1617,27 +1599,27 @@
         <v>41</v>
       </c>
       <c r="F35" s="4">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="G35" s="5">
-        <v>46287</v>
+        <v>46297</v>
       </c>
       <c r="H35" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>8298</v>
+        <v>8438</v>
       </c>
       <c r="B36" s="2">
-        <v>13144</v>
+        <v>17615</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D36" s="2">
         <v>39</v>
@@ -1646,24 +1628,24 @@
         <v>41</v>
       </c>
       <c r="F36" s="4">
-        <v>2000</v>
+        <v>120</v>
       </c>
       <c r="G36" s="5">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="H36" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>8306</v>
+        <v>8499</v>
       </c>
       <c r="B37" s="2">
-        <v>14137</v>
+        <v>20081</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>49</v>
@@ -1672,13 +1654,13 @@
         <v>39</v>
       </c>
       <c r="E37" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F37" s="4">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G37" s="5">
-        <v>46286</v>
+        <v>46297</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -1688,178 +1670,70 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
-        <v>8337</v>
-      </c>
-      <c r="B38" s="2">
-        <v>13766</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="2">
-        <v>39</v>
-      </c>
-      <c r="E38" s="2">
-        <v>41</v>
-      </c>
-      <c r="F38" s="4">
-        <v>120</v>
-      </c>
-      <c r="G38" s="5">
-        <v>46289</v>
-      </c>
-      <c r="H38" s="2">
-        <v>13</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="3"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
-        <v>8343</v>
-      </c>
-      <c r="B39" s="2">
-        <v>17953</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39" s="2">
-        <v>39</v>
-      </c>
-      <c r="E39" s="2">
-        <v>41</v>
-      </c>
-      <c r="F39" s="4">
-        <v>200</v>
-      </c>
-      <c r="G39" s="5">
-        <v>46289</v>
-      </c>
-      <c r="H39" s="2">
-        <v>0</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="3"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>8345</v>
-      </c>
-      <c r="B40" s="2">
-        <v>17845</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="2">
-        <v>39</v>
-      </c>
-      <c r="E40" s="2">
-        <v>41</v>
-      </c>
-      <c r="F40" s="4">
-        <v>200</v>
-      </c>
-      <c r="G40" s="5">
-        <v>46289</v>
-      </c>
-      <c r="H40" s="2">
-        <v>2</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="3"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
-        <v>8352</v>
-      </c>
-      <c r="B41" s="2">
-        <v>18009</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D41" s="2">
-        <v>39</v>
-      </c>
-      <c r="E41" s="2">
-        <v>41</v>
-      </c>
-      <c r="F41" s="4">
-        <v>200</v>
-      </c>
-      <c r="G41" s="5">
-        <v>46289</v>
-      </c>
-      <c r="H41" s="2">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="3"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
-        <v>8360</v>
-      </c>
-      <c r="B42" s="2">
-        <v>17952</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="2">
-        <v>39</v>
-      </c>
-      <c r="E42" s="2">
-        <v>41</v>
-      </c>
-      <c r="F42" s="4">
-        <v>200</v>
-      </c>
-      <c r="G42" s="5">
-        <v>46290</v>
-      </c>
-      <c r="H42" s="2">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="3"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <v>8361</v>
-      </c>
-      <c r="B43" s="2">
-        <v>17954</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" s="2">
-        <v>39</v>
-      </c>
-      <c r="E43" s="2">
-        <v>41</v>
-      </c>
-      <c r="F43" s="4">
-        <v>200</v>
-      </c>
-      <c r="G43" s="5">
-        <v>46293</v>
-      </c>
-      <c r="H43" s="2">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>

--- a/data-source/ordens.xlsx
+++ b/data-source/ordens.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/prompt-smart-stock-sight (4) (1)antig/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\STK\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_A83E0076CB385EDFDA183BCB61CCBEC488860D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB6E5F52-782B-4E20-817B-AA3C624C2388}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE2805D-EA3C-45B6-A79D-74D904DFFEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
   <si>
     <t>Nro.OP</t>
   </si>
@@ -52,39 +52,18 @@
     <t>Abreviação</t>
   </si>
   <si>
-    <t>SAVOY LUX PRETO</t>
-  </si>
-  <si>
     <t>GRAV</t>
   </si>
   <si>
-    <t>SAVOY BLUSH</t>
-  </si>
-  <si>
     <t>EST1</t>
   </si>
   <si>
-    <t>HELSINKI OFF WHITE - 1.2MM</t>
-  </si>
-  <si>
     <t>REV 1</t>
   </si>
   <si>
-    <t>KALAHARI CARAMELO</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>KALAHARI BEGE</t>
-  </si>
-  <si>
-    <t>KALAHARI CROMO</t>
-  </si>
-  <si>
-    <t>KALAHARI PRETO</t>
-  </si>
-  <si>
     <t>RAMA</t>
   </si>
   <si>
@@ -100,27 +79,12 @@
     <t>METALIZADO LAS VEGAS OURO LIGHT</t>
   </si>
   <si>
-    <t>CANYON LIMONCELLO</t>
-  </si>
-  <si>
     <t>RECOB</t>
   </si>
   <si>
-    <t>CORDOBA BEGE</t>
-  </si>
-  <si>
-    <t>LILLY ROSE</t>
-  </si>
-  <si>
     <t>MIRAGE OURO LIGHT</t>
   </si>
   <si>
-    <t>DENVER CANELA</t>
-  </si>
-  <si>
-    <t>MIRAGE OURO ROSADO</t>
-  </si>
-  <si>
     <t>ARUBA GLAM OURO LIGHT</t>
   </si>
   <si>
@@ -130,9 +94,6 @@
     <t>ARUBA GLAM OURO ROSADO</t>
   </si>
   <si>
-    <t>IMP DIG</t>
-  </si>
-  <si>
     <t>ARUBA GLAM BRONZE</t>
   </si>
   <si>
@@ -142,21 +103,12 @@
     <t>DELHI GLAM OURO LIGHT</t>
   </si>
   <si>
-    <t>BORGONHA WHISKY</t>
-  </si>
-  <si>
     <t>BORGONHA OURO ROSADO</t>
   </si>
   <si>
-    <t>CANYON CANELA</t>
-  </si>
-  <si>
     <t>DENVER PRETO</t>
   </si>
   <si>
-    <t>DENVER NUDE</t>
-  </si>
-  <si>
     <t>MIRAGE PRETO</t>
   </si>
   <si>
@@ -166,13 +118,127 @@
     <t>SAVOY LUX BRANCO</t>
   </si>
   <si>
-    <t>TEGUS CANELA</t>
-  </si>
-  <si>
     <t>DOHA OURO LIGHT</t>
   </si>
   <si>
     <t>NAPA VIENA PVC OFF WHITE</t>
+  </si>
+  <si>
+    <t>GR 1</t>
+  </si>
+  <si>
+    <t>CALAND</t>
+  </si>
+  <si>
+    <t>BORGONHA TITANIO</t>
+  </si>
+  <si>
+    <t>BORGONHA BRONZE</t>
+  </si>
+  <si>
+    <t>DALLAS BEGE</t>
+  </si>
+  <si>
+    <t>LENNY BEGE</t>
+  </si>
+  <si>
+    <t>NAPA BARI FOSCO CAFE</t>
+  </si>
+  <si>
+    <t>NAPA LINHO DAKAR NATURAL</t>
+  </si>
+  <si>
+    <t>NAPA OLIMPIC CAFE</t>
+  </si>
+  <si>
+    <t>OPHIDIA PRETO</t>
+  </si>
+  <si>
+    <t>OPHIDIA METAL PRATA</t>
+  </si>
+  <si>
+    <t>TABLAS NATURAL</t>
+  </si>
+  <si>
+    <t>NAMIBIA CANELA</t>
+  </si>
+  <si>
+    <t>TWIST METAL OFF WHITE/PRATA</t>
+  </si>
+  <si>
+    <t>TWIST METAL BEGE/OURO LIGHT</t>
+  </si>
+  <si>
+    <t>NAPA LINHO DAKAR BRANCO</t>
+  </si>
+  <si>
+    <t>NAPA LINHO DAKAR SALVIA</t>
+  </si>
+  <si>
+    <t>NAPA LINHO DAKAR CAFE</t>
+  </si>
+  <si>
+    <t>ARUBA BEGE</t>
+  </si>
+  <si>
+    <t>ARUBA CAMOMILA</t>
+  </si>
+  <si>
+    <t>ARUBA CONHAQUE</t>
+  </si>
+  <si>
+    <t>ARUBA CANELA</t>
+  </si>
+  <si>
+    <t>ARUBA ESPRESSO</t>
+  </si>
+  <si>
+    <t>ARUBA PRETO</t>
+  </si>
+  <si>
+    <t>JACARTA PRATA</t>
+  </si>
+  <si>
+    <t>JACARTA OURO LIGHT</t>
+  </si>
+  <si>
+    <t>JACARTA OURO ROSADO</t>
+  </si>
+  <si>
+    <t>JACARTA GRAFITE</t>
+  </si>
+  <si>
+    <t>JACARTA BRONZE</t>
+  </si>
+  <si>
+    <t>JACARTA PRETO</t>
+  </si>
+  <si>
+    <t>SEVILLA ESPRESSO</t>
+  </si>
+  <si>
+    <t>LILLY CAMOMILA</t>
+  </si>
+  <si>
+    <t>LILLY GUAVA</t>
+  </si>
+  <si>
+    <t>NAPA METAL LYON GRAFITE</t>
+  </si>
+  <si>
+    <t>NAPA MADRID ESPRESSO</t>
+  </si>
+  <si>
+    <t>NAPA MADRID CAMOMILA</t>
+  </si>
+  <si>
+    <t>NAPA MADRID NEVOA</t>
+  </si>
+  <si>
+    <t>NAPA MADRID SALVIA</t>
+  </si>
+  <si>
+    <t>NAPA MADRID GUAVA</t>
   </si>
 </sst>
 </file>
@@ -582,7 +648,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
@@ -627,13 +693,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>5704</v>
+        <v>8292</v>
       </c>
       <c r="B2" s="2">
-        <v>16630</v>
+        <v>11845</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2">
         <v>39</v>
@@ -642,27 +708,27 @@
         <v>41</v>
       </c>
       <c r="F2" s="4">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="G2" s="5">
-        <v>46104</v>
+        <v>46287</v>
       </c>
       <c r="H2" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>6474</v>
+        <v>8335</v>
       </c>
       <c r="B3" s="2">
-        <v>17183</v>
+        <v>11845</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2">
         <v>39</v>
@@ -671,27 +737,27 @@
         <v>41</v>
       </c>
       <c r="F3" s="4">
-        <v>3</v>
+        <v>336</v>
       </c>
       <c r="G3" s="5">
-        <v>46168</v>
+        <v>46290</v>
       </c>
       <c r="H3" s="2">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>6876</v>
+        <v>8343</v>
       </c>
       <c r="B4" s="2">
-        <v>15535</v>
+        <v>17953</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2">
         <v>39</v>
@@ -700,172 +766,172 @@
         <v>41</v>
       </c>
       <c r="F4" s="4">
-        <v>57.5</v>
+        <v>200</v>
       </c>
       <c r="G4" s="5">
-        <v>46190</v>
+        <v>46289</v>
       </c>
       <c r="H4" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>6911</v>
+        <v>8360</v>
       </c>
       <c r="B5" s="2">
-        <v>14180</v>
+        <v>17952</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2">
         <v>39</v>
       </c>
       <c r="E5" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="4">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="G5" s="5">
-        <v>46191</v>
+        <v>46290</v>
       </c>
       <c r="H5" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>6937</v>
+        <v>8361</v>
       </c>
       <c r="B6" s="2">
-        <v>12879</v>
+        <v>17954</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2">
         <v>39</v>
       </c>
       <c r="E6" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="4">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G6" s="5">
-        <v>46195</v>
+        <v>46293</v>
       </c>
       <c r="H6" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>6938</v>
+        <v>8362</v>
       </c>
       <c r="B7" s="2">
-        <v>12883</v>
+        <v>18000</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2">
         <v>39</v>
       </c>
       <c r="E7" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" s="4">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G7" s="5">
-        <v>46195</v>
+        <v>46293</v>
       </c>
       <c r="H7" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>6939</v>
+        <v>8365</v>
       </c>
       <c r="B8" s="2">
-        <v>12776</v>
+        <v>18014</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2">
         <v>39</v>
       </c>
       <c r="E8" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" s="4">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G8" s="5">
-        <v>46195</v>
+        <v>46294</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>6940</v>
+        <v>8367</v>
       </c>
       <c r="B9" s="2">
-        <v>12878</v>
+        <v>18016</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D9" s="2">
         <v>39</v>
       </c>
       <c r="E9" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" s="4">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G9" s="5">
-        <v>46195</v>
+        <v>46294</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>7428</v>
+        <v>8378</v>
       </c>
       <c r="B10" s="2">
-        <v>16475</v>
+        <v>11844</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2">
         <v>39</v>
@@ -874,13 +940,13 @@
         <v>41</v>
       </c>
       <c r="F10" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G10" s="5">
-        <v>46230</v>
+        <v>46295</v>
       </c>
       <c r="H10" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>10</v>
@@ -888,13 +954,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>7934</v>
+        <v>8379</v>
       </c>
       <c r="B11" s="2">
-        <v>13167</v>
+        <v>11845</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2">
         <v>39</v>
@@ -903,27 +969,27 @@
         <v>41</v>
       </c>
       <c r="F11" s="4">
-        <v>400</v>
+        <v>1440</v>
       </c>
       <c r="G11" s="5">
-        <v>46258</v>
+        <v>46295</v>
       </c>
       <c r="H11" s="2">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>8096</v>
+        <v>8381</v>
       </c>
       <c r="B12" s="2">
-        <v>17256</v>
+        <v>11846</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2">
         <v>39</v>
@@ -932,27 +998,27 @@
         <v>41</v>
       </c>
       <c r="F12" s="4">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="G12" s="5">
-        <v>46275</v>
+        <v>46295</v>
       </c>
       <c r="H12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>8098</v>
+        <v>8383</v>
       </c>
       <c r="B13" s="2">
-        <v>15534</v>
+        <v>17425</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D13" s="2">
         <v>39</v>
@@ -961,27 +1027,27 @@
         <v>41</v>
       </c>
       <c r="F13" s="4">
-        <v>201.6</v>
+        <v>1000</v>
       </c>
       <c r="G13" s="5">
-        <v>46275</v>
+        <v>46295</v>
       </c>
       <c r="H13" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>8292</v>
+        <v>8386</v>
       </c>
       <c r="B14" s="2">
-        <v>11845</v>
+        <v>15536</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2">
         <v>39</v>
@@ -990,27 +1056,27 @@
         <v>41</v>
       </c>
       <c r="F14" s="4">
-        <v>12.5</v>
+        <v>200</v>
       </c>
       <c r="G14" s="5">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="H14" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>8335</v>
+        <v>8387</v>
       </c>
       <c r="B15" s="2">
-        <v>11845</v>
+        <v>16466</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2">
         <v>39</v>
@@ -1019,27 +1085,27 @@
         <v>41</v>
       </c>
       <c r="F15" s="4">
-        <v>336</v>
+        <v>400</v>
       </c>
       <c r="G15" s="5">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="H15" s="2">
         <v>13</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>8343</v>
+        <v>8388</v>
       </c>
       <c r="B16" s="2">
-        <v>17953</v>
+        <v>16571</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D16" s="2">
         <v>39</v>
@@ -1051,24 +1117,24 @@
         <v>200</v>
       </c>
       <c r="G16" s="5">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="H16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>8360</v>
+        <v>8395</v>
       </c>
       <c r="B17" s="2">
-        <v>17952</v>
+        <v>11845</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2">
         <v>39</v>
@@ -1077,13 +1143,13 @@
         <v>41</v>
       </c>
       <c r="F17" s="4">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="G17" s="5">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="H17" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>10</v>
@@ -1091,13 +1157,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>8361</v>
+        <v>8438</v>
       </c>
       <c r="B18" s="2">
-        <v>17954</v>
+        <v>17615</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2">
         <v>39</v>
@@ -1106,56 +1172,56 @@
         <v>41</v>
       </c>
       <c r="F18" s="4">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="G18" s="5">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="H18" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>8362</v>
+        <v>8499</v>
       </c>
       <c r="B19" s="2">
-        <v>18000</v>
+        <v>20081</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D19" s="2">
         <v>39</v>
       </c>
       <c r="E19" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F19" s="4">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="G19" s="5">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="H19" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>8365</v>
+        <v>8521</v>
       </c>
       <c r="B20" s="2">
-        <v>18014</v>
+        <v>15212</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D20" s="2">
         <v>39</v>
@@ -1164,27 +1230,27 @@
         <v>41</v>
       </c>
       <c r="F20" s="4">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G20" s="5">
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="H20" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>8367</v>
+        <v>8522</v>
       </c>
       <c r="B21" s="2">
-        <v>18016</v>
+        <v>11845</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D21" s="2">
         <v>39</v>
@@ -1193,27 +1259,27 @@
         <v>41</v>
       </c>
       <c r="F21" s="4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="5">
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="H21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>8378</v>
+        <v>8523</v>
       </c>
       <c r="B22" s="2">
-        <v>11844</v>
+        <v>6395</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2">
         <v>39</v>
@@ -1222,27 +1288,27 @@
         <v>41</v>
       </c>
       <c r="F22" s="4">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="G22" s="5">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="H22" s="2">
         <v>13</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>8379</v>
+        <v>8524</v>
       </c>
       <c r="B23" s="2">
-        <v>11845</v>
+        <v>17333</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D23" s="2">
         <v>39</v>
@@ -1251,27 +1317,27 @@
         <v>41</v>
       </c>
       <c r="F23" s="4">
-        <v>1440</v>
+        <v>200</v>
       </c>
       <c r="G23" s="5">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="H23" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>8380</v>
+        <v>8525</v>
       </c>
       <c r="B24" s="2">
-        <v>30095</v>
+        <v>15361</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" s="2">
         <v>39</v>
@@ -1280,27 +1346,27 @@
         <v>41</v>
       </c>
       <c r="F24" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G24" s="5">
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="H24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>8381</v>
+        <v>8526</v>
       </c>
       <c r="B25" s="2">
-        <v>11846</v>
+        <v>17420</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D25" s="2">
         <v>39</v>
@@ -1309,27 +1375,27 @@
         <v>41</v>
       </c>
       <c r="F25" s="4">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="5">
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="H25" s="2">
         <v>0</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>8382</v>
+        <v>8527</v>
       </c>
       <c r="B26" s="2">
-        <v>16503</v>
+        <v>15534</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="D26" s="2">
         <v>39</v>
@@ -1338,27 +1404,27 @@
         <v>41</v>
       </c>
       <c r="F26" s="4">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G26" s="5">
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="H26" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>8383</v>
+        <v>8529</v>
       </c>
       <c r="B27" s="2">
-        <v>17425</v>
+        <v>16650</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D27" s="2">
         <v>39</v>
@@ -1370,24 +1436,24 @@
         <v>1000</v>
       </c>
       <c r="G27" s="5">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="H27" s="2">
         <v>13</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>8384</v>
+        <v>8530</v>
       </c>
       <c r="B28" s="2">
-        <v>17416</v>
+        <v>13144</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D28" s="2">
         <v>39</v>
@@ -1396,27 +1462,27 @@
         <v>41</v>
       </c>
       <c r="F28" s="4">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="G28" s="5">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="H28" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>8385</v>
+        <v>8531</v>
       </c>
       <c r="B29" s="2">
-        <v>17420</v>
+        <v>13334</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D29" s="2">
         <v>39</v>
@@ -1425,27 +1491,27 @@
         <v>41</v>
       </c>
       <c r="F29" s="4">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="G29" s="5">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="H29" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>8386</v>
+        <v>8532</v>
       </c>
       <c r="B30" s="2">
-        <v>15536</v>
+        <v>15247</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D30" s="2">
         <v>39</v>
@@ -1457,24 +1523,24 @@
         <v>200</v>
       </c>
       <c r="G30" s="5">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>8387</v>
+        <v>8533</v>
       </c>
       <c r="B31" s="2">
-        <v>16466</v>
+        <v>14788</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D31" s="2">
         <v>39</v>
@@ -1483,27 +1549,27 @@
         <v>41</v>
       </c>
       <c r="F31" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G31" s="5">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="H31" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>8388</v>
+        <v>8534</v>
       </c>
       <c r="B32" s="2">
-        <v>16571</v>
+        <v>15622</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D32" s="2">
         <v>39</v>
@@ -1515,24 +1581,24 @@
         <v>200</v>
       </c>
       <c r="G32" s="5">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="H32" s="2">
         <v>13</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>8389</v>
+        <v>8554</v>
       </c>
       <c r="B33" s="2">
-        <v>15709</v>
+        <v>15310</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D33" s="2">
         <v>39</v>
@@ -1541,13 +1607,13 @@
         <v>41</v>
       </c>
       <c r="F33" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G33" s="5">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="H33" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>10</v>
@@ -1555,13 +1621,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>8395</v>
+        <v>8561</v>
       </c>
       <c r="B34" s="2">
-        <v>11845</v>
+        <v>12560</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D34" s="2">
         <v>39</v>
@@ -1570,27 +1636,27 @@
         <v>41</v>
       </c>
       <c r="F34" s="4">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G34" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="H34" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>8423</v>
+        <v>8562</v>
       </c>
       <c r="B35" s="2">
-        <v>15686</v>
+        <v>12563</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D35" s="2">
         <v>39</v>
@@ -1599,24 +1665,24 @@
         <v>41</v>
       </c>
       <c r="F35" s="4">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G35" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="H35" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>8438</v>
+        <v>8568</v>
       </c>
       <c r="B36" s="2">
-        <v>17615</v>
+        <v>18047</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>48</v>
@@ -1628,24 +1694,24 @@
         <v>41</v>
       </c>
       <c r="F36" s="4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G36" s="5">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>8499</v>
+        <v>8569</v>
       </c>
       <c r="B37" s="2">
-        <v>20081</v>
+        <v>18046</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>49</v>
@@ -1654,174 +1720,658 @@
         <v>39</v>
       </c>
       <c r="E37" s="2">
+        <v>41</v>
+      </c>
+      <c r="F37" s="4">
+        <v>100</v>
+      </c>
+      <c r="G37" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>8570</v>
+      </c>
+      <c r="B38" s="2">
+        <v>18043</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="2">
+        <v>39</v>
+      </c>
+      <c r="E38" s="2">
+        <v>41</v>
+      </c>
+      <c r="F38" s="4">
+        <v>100</v>
+      </c>
+      <c r="G38" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>8571</v>
+      </c>
+      <c r="B39" s="2">
+        <v>18171</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="2">
+        <v>39</v>
+      </c>
+      <c r="E39" s="2">
+        <v>41</v>
+      </c>
+      <c r="F39" s="4">
+        <v>100</v>
+      </c>
+      <c r="G39" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>8572</v>
+      </c>
+      <c r="B40" s="2">
+        <v>18177</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="2">
+        <v>39</v>
+      </c>
+      <c r="E40" s="2">
+        <v>41</v>
+      </c>
+      <c r="F40" s="4">
+        <v>100</v>
+      </c>
+      <c r="G40" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>8573</v>
+      </c>
+      <c r="B41" s="2">
+        <v>18059</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="2">
+        <v>39</v>
+      </c>
+      <c r="E41" s="2">
+        <v>41</v>
+      </c>
+      <c r="F41" s="4">
+        <v>100</v>
+      </c>
+      <c r="G41" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>8574</v>
+      </c>
+      <c r="B42" s="2">
+        <v>18173</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="2">
+        <v>39</v>
+      </c>
+      <c r="E42" s="2">
+        <v>41</v>
+      </c>
+      <c r="F42" s="4">
+        <v>100</v>
+      </c>
+      <c r="G42" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>8575</v>
+      </c>
+      <c r="B43" s="2">
+        <v>18175</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="2">
+        <v>39</v>
+      </c>
+      <c r="E43" s="2">
+        <v>41</v>
+      </c>
+      <c r="F43" s="4">
+        <v>100</v>
+      </c>
+      <c r="G43" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>8576</v>
+      </c>
+      <c r="B44" s="2">
+        <v>18163</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="2">
+        <v>39</v>
+      </c>
+      <c r="E44" s="2">
+        <v>41</v>
+      </c>
+      <c r="F44" s="4">
+        <v>100</v>
+      </c>
+      <c r="G44" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>8577</v>
+      </c>
+      <c r="B45" s="2">
+        <v>18157</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="2">
+        <v>39</v>
+      </c>
+      <c r="E45" s="2">
+        <v>41</v>
+      </c>
+      <c r="F45" s="4">
+        <v>100</v>
+      </c>
+      <c r="G45" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H45" s="2">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>8578</v>
+      </c>
+      <c r="B46" s="2">
+        <v>18158</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="2">
+        <v>39</v>
+      </c>
+      <c r="E46" s="2">
+        <v>41</v>
+      </c>
+      <c r="F46" s="4">
+        <v>100</v>
+      </c>
+      <c r="G46" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>8579</v>
+      </c>
+      <c r="B47" s="2">
+        <v>18160</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" s="2">
+        <v>39</v>
+      </c>
+      <c r="E47" s="2">
+        <v>41</v>
+      </c>
+      <c r="F47" s="4">
+        <v>100</v>
+      </c>
+      <c r="G47" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H47" s="2">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>8580</v>
+      </c>
+      <c r="B48" s="2">
+        <v>18161</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48" s="2">
+        <v>39</v>
+      </c>
+      <c r="E48" s="2">
+        <v>41</v>
+      </c>
+      <c r="F48" s="4">
+        <v>100</v>
+      </c>
+      <c r="G48" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>8581</v>
+      </c>
+      <c r="B49" s="2">
+        <v>18162</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" s="2">
+        <v>39</v>
+      </c>
+      <c r="E49" s="2">
+        <v>41</v>
+      </c>
+      <c r="F49" s="4">
+        <v>100</v>
+      </c>
+      <c r="G49" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H49" s="2">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>8582</v>
+      </c>
+      <c r="B50" s="2">
+        <v>18048</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" s="2">
+        <v>39</v>
+      </c>
+      <c r="E50" s="2">
+        <v>41</v>
+      </c>
+      <c r="F50" s="4">
+        <v>100</v>
+      </c>
+      <c r="G50" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>8583</v>
+      </c>
+      <c r="B51" s="2">
+        <v>18180</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D51" s="2">
+        <v>39</v>
+      </c>
+      <c r="E51" s="2">
+        <v>41</v>
+      </c>
+      <c r="F51" s="4">
+        <v>200</v>
+      </c>
+      <c r="G51" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H51" s="2">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>8584</v>
+      </c>
+      <c r="B52" s="2">
+        <v>18039</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" s="2">
+        <v>39</v>
+      </c>
+      <c r="E52" s="2">
+        <v>41</v>
+      </c>
+      <c r="F52" s="4">
+        <v>100</v>
+      </c>
+      <c r="G52" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H52" s="2">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>8585</v>
+      </c>
+      <c r="B53" s="2">
+        <v>18041</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" s="2">
+        <v>39</v>
+      </c>
+      <c r="E53" s="2">
+        <v>41</v>
+      </c>
+      <c r="F53" s="4">
+        <v>100</v>
+      </c>
+      <c r="G53" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>8586</v>
+      </c>
+      <c r="B54" s="2">
+        <v>18198</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D54" s="2">
+        <v>39</v>
+      </c>
+      <c r="E54" s="2">
+        <v>41</v>
+      </c>
+      <c r="F54" s="4">
+        <v>400</v>
+      </c>
+      <c r="G54" s="5">
+        <v>46303</v>
+      </c>
+      <c r="H54" s="2">
+        <v>1</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>8597</v>
+      </c>
+      <c r="B55" s="2">
+        <v>17899</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" s="2">
+        <v>39</v>
+      </c>
+      <c r="E55" s="2">
+        <v>41</v>
+      </c>
+      <c r="F55" s="4">
         <v>40</v>
       </c>
-      <c r="F37" s="4">
-        <v>50</v>
-      </c>
-      <c r="G37" s="5">
-        <v>46297</v>
-      </c>
-      <c r="H37" s="2">
-        <v>0</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="3"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="3"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="3"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="3"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="3"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="3"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="3"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="3"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="3"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="3"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="3"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="3"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="3"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="3"/>
+      <c r="G55" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H55" s="2">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>8598</v>
+      </c>
+      <c r="B56" s="2">
+        <v>17918</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="2">
+        <v>39</v>
+      </c>
+      <c r="E56" s="2">
+        <v>41</v>
+      </c>
+      <c r="F56" s="4">
+        <v>40</v>
+      </c>
+      <c r="G56" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H56" s="2">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>8599</v>
+      </c>
+      <c r="B57" s="2">
+        <v>18012</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" s="2">
+        <v>39</v>
+      </c>
+      <c r="E57" s="2">
+        <v>41</v>
+      </c>
+      <c r="F57" s="4">
+        <v>100</v>
+      </c>
+      <c r="G57" s="5">
+        <v>46304</v>
+      </c>
+      <c r="H57" s="2">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>8601</v>
+      </c>
+      <c r="B58" s="2">
+        <v>18214</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="2">
+        <v>39</v>
+      </c>
+      <c r="E58" s="2">
+        <v>41</v>
+      </c>
+      <c r="F58" s="4">
+        <v>100</v>
+      </c>
+      <c r="G58" s="5">
+        <v>46307</v>
+      </c>
+      <c r="H58" s="2">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>8602</v>
+      </c>
+      <c r="B59" s="2">
+        <v>17900</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D59" s="2">
+        <v>39</v>
+      </c>
+      <c r="E59" s="2">
+        <v>41</v>
+      </c>
+      <c r="F59" s="4">
+        <v>40</v>
+      </c>
+      <c r="G59" s="5">
+        <v>46307</v>
+      </c>
+      <c r="H59" s="2">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <printOptions gridLines="1"/>

--- a/data-source/ordens.xlsx
+++ b/data-source/ordens.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\STK\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/STK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE2805D-EA3C-45B6-A79D-74D904DFFEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{6DE2805D-EA3C-45B6-A79D-74D904DFFEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5496510-6F94-481A-AEA2-8F2E39177CD7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="72">
   <si>
     <t>Nro.OP</t>
   </si>
@@ -64,18 +64,12 @@
     <t/>
   </si>
   <si>
-    <t>RAMA</t>
-  </si>
-  <si>
     <t>BORGONHA OURO LIGHT</t>
   </si>
   <si>
     <t>JUMBO 1</t>
   </si>
   <si>
-    <t>BORGONHA PRATA</t>
-  </si>
-  <si>
     <t>METALIZADO LAS VEGAS OURO LIGHT</t>
   </si>
   <si>
@@ -85,33 +79,15 @@
     <t>MIRAGE OURO LIGHT</t>
   </si>
   <si>
-    <t>ARUBA GLAM OURO LIGHT</t>
-  </si>
-  <si>
-    <t>ARUBA GLAM PRATA</t>
-  </si>
-  <si>
-    <t>ARUBA GLAM OURO ROSADO</t>
-  </si>
-  <si>
-    <t>ARUBA GLAM BRONZE</t>
-  </si>
-  <si>
     <t>DELHI GLAM PRATA</t>
   </si>
   <si>
     <t>DELHI GLAM OURO LIGHT</t>
   </si>
   <si>
-    <t>BORGONHA OURO ROSADO</t>
-  </si>
-  <si>
     <t>DENVER PRETO</t>
   </si>
   <si>
-    <t>MIRAGE PRETO</t>
-  </si>
-  <si>
     <t>SAVOY GLAM OURO LIGHT</t>
   </si>
   <si>
@@ -127,57 +103,21 @@
     <t>GR 1</t>
   </si>
   <si>
-    <t>CALAND</t>
-  </si>
-  <si>
     <t>BORGONHA TITANIO</t>
   </si>
   <si>
-    <t>BORGONHA BRONZE</t>
-  </si>
-  <si>
-    <t>DALLAS BEGE</t>
-  </si>
-  <si>
-    <t>LENNY BEGE</t>
-  </si>
-  <si>
     <t>NAPA BARI FOSCO CAFE</t>
   </si>
   <si>
     <t>NAPA LINHO DAKAR NATURAL</t>
   </si>
   <si>
-    <t>NAPA OLIMPIC CAFE</t>
-  </si>
-  <si>
-    <t>OPHIDIA PRETO</t>
-  </si>
-  <si>
-    <t>OPHIDIA METAL PRATA</t>
-  </si>
-  <si>
-    <t>TABLAS NATURAL</t>
-  </si>
-  <si>
-    <t>NAMIBIA CANELA</t>
-  </si>
-  <si>
     <t>TWIST METAL OFF WHITE/PRATA</t>
   </si>
   <si>
-    <t>TWIST METAL BEGE/OURO LIGHT</t>
-  </si>
-  <si>
     <t>NAPA LINHO DAKAR BRANCO</t>
   </si>
   <si>
-    <t>NAPA LINHO DAKAR SALVIA</t>
-  </si>
-  <si>
-    <t>NAPA LINHO DAKAR CAFE</t>
-  </si>
-  <si>
     <t>ARUBA BEGE</t>
   </si>
   <si>
@@ -239,6 +179,66 @@
   </si>
   <si>
     <t>NAPA MADRID GUAVA</t>
+  </si>
+  <si>
+    <t>SAVOY LUX PRETO</t>
+  </si>
+  <si>
+    <t>SAVOY BLUSH</t>
+  </si>
+  <si>
+    <t>HELSINKI OFF WHITE - 1.2MM</t>
+  </si>
+  <si>
+    <t>KALAHARI CARAMELO</t>
+  </si>
+  <si>
+    <t>KALAHARI BEGE</t>
+  </si>
+  <si>
+    <t>KALAHARI CROMO</t>
+  </si>
+  <si>
+    <t>KALAHARI PRETO</t>
+  </si>
+  <si>
+    <t>CANYON LIMONCELLO</t>
+  </si>
+  <si>
+    <t>CORDOBA BEGE</t>
+  </si>
+  <si>
+    <t>ESTAM</t>
+  </si>
+  <si>
+    <t>REC2</t>
+  </si>
+  <si>
+    <t>CANYON CONHAQUE</t>
+  </si>
+  <si>
+    <t>MACKAY GLAM OURO LIGHT</t>
+  </si>
+  <si>
+    <t>MIRAGE OURO ROSADO</t>
+  </si>
+  <si>
+    <t>NAPA FLOATER VENEZIA DOURADO</t>
+  </si>
+  <si>
+    <t>OREGON OFF WHITE</t>
+  </si>
+  <si>
+    <t>OREGON BEGE</t>
+  </si>
+  <si>
+    <t>OREGON CONHAQUE</t>
+  </si>
+  <si>
+    <t>OREGON CAFE</t>
+  </si>
+  <si>
+    <t>OREGON PRETO</t>
   </si>
 </sst>
 </file>
@@ -648,7 +648,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
@@ -693,13 +693,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>8292</v>
+        <v>5704</v>
       </c>
       <c r="B2" s="2">
-        <v>11845</v>
+        <v>16630</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2">
         <v>39</v>
@@ -708,27 +708,27 @@
         <v>41</v>
       </c>
       <c r="F2" s="4">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="G2" s="5">
-        <v>46287</v>
+        <v>46104</v>
       </c>
       <c r="H2" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>8335</v>
+        <v>6474</v>
       </c>
       <c r="B3" s="2">
-        <v>11845</v>
+        <v>17183</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2">
         <v>39</v>
@@ -737,155 +737,155 @@
         <v>41</v>
       </c>
       <c r="F3" s="4">
-        <v>336</v>
+        <v>3</v>
       </c>
       <c r="G3" s="5">
-        <v>46290</v>
+        <v>46168</v>
       </c>
       <c r="H3" s="2">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>8343</v>
+        <v>6911</v>
       </c>
       <c r="B4" s="2">
-        <v>17953</v>
+        <v>14180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2">
         <v>39</v>
       </c>
       <c r="E4" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4" s="4">
-        <v>200</v>
+        <v>132</v>
       </c>
       <c r="G4" s="5">
-        <v>46289</v>
+        <v>46191</v>
       </c>
       <c r="H4" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>8360</v>
+        <v>6937</v>
       </c>
       <c r="B5" s="2">
-        <v>17952</v>
+        <v>12879</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2">
         <v>39</v>
       </c>
       <c r="E5" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5" s="4">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="G5" s="5">
-        <v>46290</v>
+        <v>46195</v>
       </c>
       <c r="H5" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>8361</v>
+        <v>6938</v>
       </c>
       <c r="B6" s="2">
-        <v>17954</v>
+        <v>12883</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2">
         <v>39</v>
       </c>
       <c r="E6" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="4">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="G6" s="5">
-        <v>46293</v>
+        <v>46195</v>
       </c>
       <c r="H6" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>8362</v>
+        <v>6939</v>
       </c>
       <c r="B7" s="2">
-        <v>18000</v>
+        <v>12776</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2">
         <v>39</v>
       </c>
       <c r="E7" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" s="4">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="G7" s="5">
-        <v>46293</v>
+        <v>46195</v>
       </c>
       <c r="H7" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>8365</v>
+        <v>6940</v>
       </c>
       <c r="B8" s="2">
-        <v>18014</v>
+        <v>12878</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2">
         <v>39</v>
       </c>
       <c r="E8" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" s="4">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="G8" s="5">
-        <v>46294</v>
+        <v>46195</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -896,13 +896,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>8367</v>
+        <v>7428</v>
       </c>
       <c r="B9" s="2">
-        <v>18016</v>
+        <v>16475</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D9" s="2">
         <v>39</v>
@@ -911,27 +911,27 @@
         <v>41</v>
       </c>
       <c r="F9" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G9" s="5">
-        <v>46294</v>
+        <v>46230</v>
       </c>
       <c r="H9" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>8378</v>
+        <v>7934</v>
       </c>
       <c r="B10" s="2">
-        <v>11844</v>
+        <v>13167</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D10" s="2">
         <v>39</v>
@@ -940,27 +940,27 @@
         <v>41</v>
       </c>
       <c r="F10" s="4">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="G10" s="5">
-        <v>46295</v>
+        <v>46258</v>
       </c>
       <c r="H10" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>8379</v>
+        <v>8292</v>
       </c>
       <c r="B11" s="2">
         <v>11845</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2">
         <v>39</v>
@@ -969,27 +969,27 @@
         <v>41</v>
       </c>
       <c r="F11" s="4">
-        <v>1440</v>
+        <v>12.5</v>
       </c>
       <c r="G11" s="5">
-        <v>46295</v>
+        <v>46287</v>
       </c>
       <c r="H11" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>8381</v>
+        <v>8335</v>
       </c>
       <c r="B12" s="2">
-        <v>11846</v>
+        <v>11845</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2">
         <v>39</v>
@@ -998,27 +998,27 @@
         <v>41</v>
       </c>
       <c r="F12" s="4">
-        <v>600</v>
+        <v>336</v>
       </c>
       <c r="G12" s="5">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>8383</v>
+        <v>8365</v>
       </c>
       <c r="B13" s="2">
-        <v>17425</v>
+        <v>18014</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D13" s="2">
         <v>39</v>
@@ -1027,27 +1027,27 @@
         <v>41</v>
       </c>
       <c r="F13" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G13" s="5">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="H13" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>8386</v>
+        <v>8367</v>
       </c>
       <c r="B14" s="2">
-        <v>15536</v>
+        <v>18016</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D14" s="2">
         <v>39</v>
@@ -1059,24 +1059,24 @@
         <v>200</v>
       </c>
       <c r="G14" s="5">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="H14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>8387</v>
+        <v>8383</v>
       </c>
       <c r="B15" s="2">
-        <v>16466</v>
+        <v>17425</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D15" s="2">
         <v>39</v>
@@ -1085,7 +1085,7 @@
         <v>41</v>
       </c>
       <c r="F15" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G15" s="5">
         <v>46295</v>
@@ -1094,18 +1094,18 @@
         <v>13</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>8388</v>
+        <v>8387</v>
       </c>
       <c r="B16" s="2">
-        <v>16571</v>
+        <v>16466</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D16" s="2">
         <v>39</v>
@@ -1114,27 +1114,27 @@
         <v>41</v>
       </c>
       <c r="F16" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G16" s="5">
         <v>46295</v>
       </c>
       <c r="H16" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>8395</v>
+        <v>8388</v>
       </c>
       <c r="B17" s="2">
-        <v>11845</v>
+        <v>16571</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D17" s="2">
         <v>39</v>
@@ -1143,27 +1143,27 @@
         <v>41</v>
       </c>
       <c r="F17" s="4">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G17" s="5">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="H17" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>8438</v>
+        <v>8395</v>
       </c>
       <c r="B18" s="2">
-        <v>17615</v>
+        <v>11845</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2">
         <v>39</v>
@@ -1172,74 +1172,74 @@
         <v>41</v>
       </c>
       <c r="F18" s="4">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G18" s="5">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="H18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>8499</v>
+        <v>8438</v>
       </c>
       <c r="B19" s="2">
-        <v>20081</v>
+        <v>17615</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D19" s="2">
         <v>39</v>
       </c>
       <c r="E19" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F19" s="4">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="G19" s="5">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="H19" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>8521</v>
+        <v>8499</v>
       </c>
       <c r="B20" s="2">
-        <v>15212</v>
+        <v>20081</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D20" s="2">
         <v>39</v>
       </c>
       <c r="E20" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F20" s="4">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="G20" s="5">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="H20" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1250,7 +1250,7 @@
         <v>11845</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2">
         <v>39</v>
@@ -1265,21 +1265,21 @@
         <v>46302</v>
       </c>
       <c r="H21" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>8523</v>
+        <v>8526</v>
       </c>
       <c r="B22" s="2">
-        <v>6395</v>
+        <v>17420</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D22" s="2">
         <v>39</v>
@@ -1288,27 +1288,27 @@
         <v>41</v>
       </c>
       <c r="F22" s="4">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="G22" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H22" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>8524</v>
+        <v>8527</v>
       </c>
       <c r="B23" s="2">
-        <v>17333</v>
+        <v>15534</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D23" s="2">
         <v>39</v>
@@ -1317,27 +1317,27 @@
         <v>41</v>
       </c>
       <c r="F23" s="4">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G23" s="5">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H23" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>8525</v>
+        <v>8530</v>
       </c>
       <c r="B24" s="2">
-        <v>15361</v>
+        <v>13144</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D24" s="2">
         <v>39</v>
@@ -1346,27 +1346,27 @@
         <v>41</v>
       </c>
       <c r="F24" s="4">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="G24" s="5">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H24" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>8526</v>
+        <v>8561</v>
       </c>
       <c r="B25" s="2">
-        <v>17420</v>
+        <v>12560</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2">
         <v>39</v>
@@ -1375,27 +1375,27 @@
         <v>41</v>
       </c>
       <c r="F25" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G25" s="5">
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="H25" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>8527</v>
+        <v>8568</v>
       </c>
       <c r="B26" s="2">
-        <v>15534</v>
+        <v>18047</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D26" s="2">
         <v>39</v>
@@ -1404,27 +1404,27 @@
         <v>41</v>
       </c>
       <c r="F26" s="4">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G26" s="5">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H26" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>8529</v>
+        <v>8571</v>
       </c>
       <c r="B27" s="2">
-        <v>16650</v>
+        <v>18171</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D27" s="2">
         <v>39</v>
@@ -1433,27 +1433,27 @@
         <v>41</v>
       </c>
       <c r="F27" s="4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G27" s="5">
         <v>46304</v>
       </c>
       <c r="H27" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>8530</v>
+        <v>8572</v>
       </c>
       <c r="B28" s="2">
-        <v>13144</v>
+        <v>18177</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D28" s="2">
         <v>39</v>
@@ -1462,27 +1462,27 @@
         <v>41</v>
       </c>
       <c r="F28" s="4">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="G28" s="5">
         <v>46304</v>
       </c>
       <c r="H28" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>8531</v>
+        <v>8573</v>
       </c>
       <c r="B29" s="2">
-        <v>13334</v>
+        <v>18059</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D29" s="2">
         <v>39</v>
@@ -1491,27 +1491,27 @@
         <v>41</v>
       </c>
       <c r="F29" s="4">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="G29" s="5">
         <v>46304</v>
       </c>
       <c r="H29" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>8532</v>
+        <v>8574</v>
       </c>
       <c r="B30" s="2">
-        <v>15247</v>
+        <v>18173</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D30" s="2">
         <v>39</v>
@@ -1520,27 +1520,27 @@
         <v>41</v>
       </c>
       <c r="F30" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G30" s="5">
         <v>46304</v>
       </c>
       <c r="H30" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>8533</v>
+        <v>8575</v>
       </c>
       <c r="B31" s="2">
-        <v>14788</v>
+        <v>18175</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D31" s="2">
         <v>39</v>
@@ -1549,27 +1549,27 @@
         <v>41</v>
       </c>
       <c r="F31" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G31" s="5">
         <v>46304</v>
       </c>
       <c r="H31" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>8534</v>
+        <v>8576</v>
       </c>
       <c r="B32" s="2">
-        <v>15622</v>
+        <v>18163</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D32" s="2">
         <v>39</v>
@@ -1578,27 +1578,27 @@
         <v>41</v>
       </c>
       <c r="F32" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G32" s="5">
         <v>46304</v>
       </c>
       <c r="H32" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>8554</v>
+        <v>8577</v>
       </c>
       <c r="B33" s="2">
-        <v>15310</v>
+        <v>18157</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D33" s="2">
         <v>39</v>
@@ -1607,27 +1607,27 @@
         <v>41</v>
       </c>
       <c r="F33" s="4">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G33" s="5">
-        <v>46301</v>
+        <v>46304</v>
       </c>
       <c r="H33" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>8561</v>
+        <v>8578</v>
       </c>
       <c r="B34" s="2">
-        <v>12560</v>
+        <v>18158</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D34" s="2">
         <v>39</v>
@@ -1636,27 +1636,27 @@
         <v>41</v>
       </c>
       <c r="F34" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G34" s="5">
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="H34" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>8562</v>
+        <v>8579</v>
       </c>
       <c r="B35" s="2">
-        <v>12563</v>
+        <v>18160</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D35" s="2">
         <v>39</v>
@@ -1665,10 +1665,10 @@
         <v>41</v>
       </c>
       <c r="F35" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G35" s="5">
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="H35" s="2">
         <v>0</v>
@@ -1679,13 +1679,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>8568</v>
+        <v>8580</v>
       </c>
       <c r="B36" s="2">
-        <v>18047</v>
+        <v>18161</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D36" s="2">
         <v>39</v>
@@ -1700,21 +1700,21 @@
         <v>46304</v>
       </c>
       <c r="H36" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>8569</v>
+        <v>8581</v>
       </c>
       <c r="B37" s="2">
-        <v>18046</v>
+        <v>18162</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D37" s="2">
         <v>39</v>
@@ -1729,21 +1729,21 @@
         <v>46304</v>
       </c>
       <c r="H37" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>8570</v>
+        <v>8582</v>
       </c>
       <c r="B38" s="2">
-        <v>18043</v>
+        <v>18048</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D38" s="2">
         <v>39</v>
@@ -1758,21 +1758,21 @@
         <v>46304</v>
       </c>
       <c r="H38" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>8571</v>
+        <v>8583</v>
       </c>
       <c r="B39" s="2">
-        <v>18171</v>
+        <v>18180</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D39" s="2">
         <v>39</v>
@@ -1781,27 +1781,27 @@
         <v>41</v>
       </c>
       <c r="F39" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G39" s="5">
         <v>46304</v>
       </c>
       <c r="H39" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>8572</v>
+        <v>8584</v>
       </c>
       <c r="B40" s="2">
-        <v>18177</v>
+        <v>18039</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D40" s="2">
         <v>39</v>
@@ -1824,13 +1824,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>8573</v>
+        <v>8585</v>
       </c>
       <c r="B41" s="2">
-        <v>18059</v>
+        <v>18041</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D41" s="2">
         <v>39</v>
@@ -1853,13 +1853,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>8574</v>
+        <v>8586</v>
       </c>
       <c r="B42" s="2">
-        <v>18173</v>
+        <v>18198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D42" s="2">
         <v>39</v>
@@ -1868,27 +1868,27 @@
         <v>41</v>
       </c>
       <c r="F42" s="4">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G42" s="5">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>8575</v>
+        <v>8597</v>
       </c>
       <c r="B43" s="2">
-        <v>18175</v>
+        <v>17899</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D43" s="2">
         <v>39</v>
@@ -1897,27 +1897,27 @@
         <v>41</v>
       </c>
       <c r="F43" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G43" s="5">
         <v>46304</v>
       </c>
       <c r="H43" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>8576</v>
+        <v>8598</v>
       </c>
       <c r="B44" s="2">
-        <v>18163</v>
+        <v>17918</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D44" s="2">
         <v>39</v>
@@ -1926,27 +1926,27 @@
         <v>41</v>
       </c>
       <c r="F44" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G44" s="5">
         <v>46304</v>
       </c>
       <c r="H44" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>8577</v>
+        <v>8599</v>
       </c>
       <c r="B45" s="2">
-        <v>18157</v>
+        <v>18012</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D45" s="2">
         <v>39</v>
@@ -1961,21 +1961,21 @@
         <v>46304</v>
       </c>
       <c r="H45" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>8578</v>
+        <v>8601</v>
       </c>
       <c r="B46" s="2">
-        <v>18158</v>
+        <v>18214</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D46" s="2">
         <v>39</v>
@@ -1987,24 +1987,24 @@
         <v>100</v>
       </c>
       <c r="G46" s="5">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="H46" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>8579</v>
+        <v>8602</v>
       </c>
       <c r="B47" s="2">
-        <v>18160</v>
+        <v>17900</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D47" s="2">
         <v>39</v>
@@ -2013,27 +2013,27 @@
         <v>41</v>
       </c>
       <c r="F47" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G47" s="5">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="H47" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>8580</v>
+        <v>8633</v>
       </c>
       <c r="B48" s="2">
-        <v>18161</v>
+        <v>15212</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D48" s="2">
         <v>39</v>
@@ -2042,10 +2042,10 @@
         <v>41</v>
       </c>
       <c r="F48" s="4">
-        <v>100</v>
+        <v>528</v>
       </c>
       <c r="G48" s="5">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -2056,13 +2056,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>8581</v>
+        <v>8634</v>
       </c>
       <c r="B49" s="2">
-        <v>18162</v>
+        <v>11845</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="D49" s="2">
         <v>39</v>
@@ -2071,27 +2071,27 @@
         <v>41</v>
       </c>
       <c r="F49" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G49" s="5">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="H49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>8582</v>
+        <v>8635</v>
       </c>
       <c r="B50" s="2">
-        <v>18048</v>
+        <v>17271</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D50" s="2">
         <v>39</v>
@@ -2100,27 +2100,27 @@
         <v>41</v>
       </c>
       <c r="F50" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G50" s="5">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="H50" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>8583</v>
+        <v>8637</v>
       </c>
       <c r="B51" s="2">
-        <v>18180</v>
+        <v>17322</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D51" s="2">
         <v>39</v>
@@ -2129,27 +2129,27 @@
         <v>41</v>
       </c>
       <c r="F51" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G51" s="5">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="H51" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>8584</v>
+        <v>8638</v>
       </c>
       <c r="B52" s="2">
-        <v>18039</v>
+        <v>17420</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="D52" s="2">
         <v>39</v>
@@ -2158,24 +2158,24 @@
         <v>41</v>
       </c>
       <c r="F52" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G52" s="5">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="H52" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>8585</v>
+        <v>8639</v>
       </c>
       <c r="B53" s="2">
-        <v>18041</v>
+        <v>15535</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>65</v>
@@ -2187,10 +2187,10 @@
         <v>41</v>
       </c>
       <c r="F53" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G53" s="5">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>8586</v>
+        <v>8641</v>
       </c>
       <c r="B54" s="2">
-        <v>18198</v>
+        <v>16605</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>66</v>
@@ -2216,27 +2216,27 @@
         <v>41</v>
       </c>
       <c r="F54" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G54" s="5">
-        <v>46303</v>
+        <v>46309</v>
       </c>
       <c r="H54" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>8597</v>
+        <v>8644</v>
       </c>
       <c r="B55" s="2">
-        <v>17899</v>
+        <v>16650</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="D55" s="2">
         <v>39</v>
@@ -2245,10 +2245,10 @@
         <v>41</v>
       </c>
       <c r="F55" s="4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="G55" s="5">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2259,13 +2259,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>8598</v>
+        <v>8702</v>
       </c>
       <c r="B56" s="2">
-        <v>17918</v>
+        <v>18230</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56" s="2">
         <v>39</v>
@@ -2277,7 +2277,7 @@
         <v>40</v>
       </c>
       <c r="G56" s="5">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
@@ -2288,13 +2288,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>8599</v>
+        <v>8703</v>
       </c>
       <c r="B57" s="2">
-        <v>18012</v>
+        <v>18232</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D57" s="2">
         <v>39</v>
@@ -2303,10 +2303,10 @@
         <v>41</v>
       </c>
       <c r="F57" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G57" s="5">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2317,13 +2317,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>8601</v>
+        <v>8704</v>
       </c>
       <c r="B58" s="2">
-        <v>18214</v>
+        <v>18228</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D58" s="2">
         <v>39</v>
@@ -2332,10 +2332,10 @@
         <v>41</v>
       </c>
       <c r="F58" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G58" s="5">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -2346,13 +2346,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>8602</v>
+        <v>8705</v>
       </c>
       <c r="B59" s="2">
-        <v>17900</v>
+        <v>18226</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D59" s="2">
         <v>39</v>
@@ -2364,12 +2364,41 @@
         <v>40</v>
       </c>
       <c r="G59" s="5">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
       </c>
       <c r="I59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>8707</v>
+      </c>
+      <c r="B60" s="2">
+        <v>18233</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D60" s="2">
+        <v>39</v>
+      </c>
+      <c r="E60" s="2">
+        <v>41</v>
+      </c>
+      <c r="F60" s="4">
+        <v>40</v>
+      </c>
+      <c r="G60" s="5">
+        <v>46311</v>
+      </c>
+      <c r="H60" s="2">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/data-source/ordens.xlsx
+++ b/data-source/ordens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/STK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{6DE2805D-EA3C-45B6-A79D-74D904DFFEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5496510-6F94-481A-AEA2-8F2E39177CD7}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{6DE2805D-EA3C-45B6-A79D-74D904DFFEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A2FA923-49C6-47C0-AF35-5AAEE481C6F2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="76">
   <si>
     <t>Nro.OP</t>
   </si>
@@ -73,18 +73,12 @@
     <t>METALIZADO LAS VEGAS OURO LIGHT</t>
   </si>
   <si>
-    <t>RECOB</t>
-  </si>
-  <si>
     <t>MIRAGE OURO LIGHT</t>
   </si>
   <si>
     <t>DELHI GLAM PRATA</t>
   </si>
   <si>
-    <t>DELHI GLAM OURO LIGHT</t>
-  </si>
-  <si>
     <t>DENVER PRETO</t>
   </si>
   <si>
@@ -106,18 +100,9 @@
     <t>BORGONHA TITANIO</t>
   </si>
   <si>
-    <t>NAPA BARI FOSCO CAFE</t>
-  </si>
-  <si>
     <t>NAPA LINHO DAKAR NATURAL</t>
   </si>
   <si>
-    <t>TWIST METAL OFF WHITE/PRATA</t>
-  </si>
-  <si>
-    <t>NAPA LINHO DAKAR BRANCO</t>
-  </si>
-  <si>
     <t>ARUBA BEGE</t>
   </si>
   <si>
@@ -223,9 +208,6 @@
     <t>MIRAGE OURO ROSADO</t>
   </si>
   <si>
-    <t>NAPA FLOATER VENEZIA DOURADO</t>
-  </si>
-  <si>
     <t>OREGON OFF WHITE</t>
   </si>
   <si>
@@ -239,6 +221,36 @@
   </si>
   <si>
     <t>OREGON PRETO</t>
+  </si>
+  <si>
+    <t>CANYON CAMOMILA</t>
+  </si>
+  <si>
+    <t>CANYON SALVIA</t>
+  </si>
+  <si>
+    <t>CANYON GUAVA</t>
+  </si>
+  <si>
+    <t>CANYON ESPRESSO</t>
+  </si>
+  <si>
+    <t>BORGONHA WHISKY</t>
+  </si>
+  <si>
+    <t>CANYON CANELA</t>
+  </si>
+  <si>
+    <t>LILLY BRANCO</t>
+  </si>
+  <si>
+    <t>SAVOY GLAM PRATA</t>
+  </si>
+  <si>
+    <t>STELLAR OFF WHITE</t>
+  </si>
+  <si>
+    <t>STELLAR ROSE</t>
   </si>
 </sst>
 </file>
@@ -262,6 +274,7 @@
       <sz val="11"/>
       <color rgb="FF800000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -326,6 +339,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -648,7 +665,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
@@ -699,7 +716,7 @@
         <v>16630</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2">
         <v>39</v>
@@ -728,7 +745,7 @@
         <v>17183</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2">
         <v>39</v>
@@ -757,7 +774,7 @@
         <v>14180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2">
         <v>39</v>
@@ -786,7 +803,7 @@
         <v>12879</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2">
         <v>39</v>
@@ -815,7 +832,7 @@
         <v>12883</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2">
         <v>39</v>
@@ -844,7 +861,7 @@
         <v>12776</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D7" s="2">
         <v>39</v>
@@ -873,7 +890,7 @@
         <v>12878</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D8" s="2">
         <v>39</v>
@@ -902,7 +919,7 @@
         <v>16475</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2">
         <v>39</v>
@@ -931,7 +948,7 @@
         <v>13167</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D10" s="2">
         <v>39</v>
@@ -946,10 +963,10 @@
         <v>46258</v>
       </c>
       <c r="H10" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -983,13 +1000,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>8335</v>
+        <v>8365</v>
       </c>
       <c r="B12" s="2">
-        <v>11845</v>
+        <v>18014</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2">
         <v>39</v>
@@ -998,24 +1015,24 @@
         <v>41</v>
       </c>
       <c r="F12" s="4">
-        <v>336</v>
+        <v>200</v>
       </c>
       <c r="G12" s="5">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="H12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>8365</v>
+        <v>8383</v>
       </c>
       <c r="B13" s="2">
-        <v>18014</v>
+        <v>17425</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>18</v>
@@ -1027,27 +1044,27 @@
         <v>41</v>
       </c>
       <c r="F13" s="4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G13" s="5">
-        <v>46294</v>
+        <v>46315</v>
       </c>
       <c r="H13" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>8367</v>
+        <v>8388</v>
       </c>
       <c r="B14" s="2">
-        <v>18016</v>
+        <v>16571</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="2">
         <v>39</v>
@@ -1059,24 +1076,24 @@
         <v>200</v>
       </c>
       <c r="G14" s="5">
-        <v>46294</v>
+        <v>46314</v>
       </c>
       <c r="H14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>8383</v>
+        <v>8438</v>
       </c>
       <c r="B15" s="2">
-        <v>17425</v>
+        <v>17615</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" s="2">
         <v>39</v>
@@ -1085,56 +1102,56 @@
         <v>41</v>
       </c>
       <c r="F15" s="4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="G15" s="5">
         <v>46295</v>
       </c>
       <c r="H15" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>8387</v>
+        <v>8499</v>
       </c>
       <c r="B16" s="2">
-        <v>16466</v>
+        <v>20081</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="2">
         <v>39</v>
       </c>
       <c r="E16" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" s="4">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="G16" s="5">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="H16" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>8388</v>
+        <v>8527</v>
       </c>
       <c r="B17" s="2">
-        <v>16571</v>
+        <v>15534</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D17" s="2">
         <v>39</v>
@@ -1143,27 +1160,27 @@
         <v>41</v>
       </c>
       <c r="F17" s="4">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G17" s="5">
-        <v>46295</v>
+        <v>46318</v>
       </c>
       <c r="H17" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>8395</v>
+        <v>8530</v>
       </c>
       <c r="B18" s="2">
-        <v>11845</v>
+        <v>13144</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D18" s="2">
         <v>39</v>
@@ -1172,27 +1189,27 @@
         <v>41</v>
       </c>
       <c r="F18" s="4">
-        <v>240</v>
+        <v>1668</v>
       </c>
       <c r="G18" s="5">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="H18" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>8438</v>
+        <v>8571</v>
       </c>
       <c r="B19" s="2">
-        <v>17615</v>
+        <v>18171</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D19" s="2">
         <v>39</v>
@@ -1201,10 +1218,10 @@
         <v>41</v>
       </c>
       <c r="F19" s="4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G19" s="5">
-        <v>46295</v>
+        <v>46318</v>
       </c>
       <c r="H19" s="2">
         <v>2</v>
@@ -1215,42 +1232,42 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>8499</v>
+        <v>8572</v>
       </c>
       <c r="B20" s="2">
-        <v>20081</v>
+        <v>18177</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D20" s="2">
         <v>39</v>
       </c>
       <c r="E20" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F20" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G20" s="5">
-        <v>46297</v>
+        <v>46318</v>
       </c>
       <c r="H20" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>8522</v>
+        <v>8573</v>
       </c>
       <c r="B21" s="2">
-        <v>11845</v>
+        <v>18059</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D21" s="2">
         <v>39</v>
@@ -1259,27 +1276,27 @@
         <v>41</v>
       </c>
       <c r="F21" s="4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G21" s="5">
-        <v>46302</v>
+        <v>46318</v>
       </c>
       <c r="H21" s="2">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>8526</v>
+        <v>8574</v>
       </c>
       <c r="B22" s="2">
-        <v>17420</v>
+        <v>18173</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D22" s="2">
         <v>39</v>
@@ -1288,27 +1305,27 @@
         <v>41</v>
       </c>
       <c r="F22" s="4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G22" s="5">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H22" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>8527</v>
+        <v>8575</v>
       </c>
       <c r="B23" s="2">
-        <v>15534</v>
+        <v>18175</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D23" s="2">
         <v>39</v>
@@ -1317,27 +1334,27 @@
         <v>41</v>
       </c>
       <c r="F23" s="4">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="G23" s="5">
-        <v>46303</v>
+        <v>46318</v>
       </c>
       <c r="H23" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>8530</v>
+        <v>8576</v>
       </c>
       <c r="B24" s="2">
-        <v>13144</v>
+        <v>18163</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D24" s="2">
         <v>39</v>
@@ -1346,10 +1363,10 @@
         <v>41</v>
       </c>
       <c r="F24" s="4">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="G24" s="5">
-        <v>46304</v>
+        <v>46318</v>
       </c>
       <c r="H24" s="2">
         <v>2</v>
@@ -1360,13 +1377,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>8561</v>
+        <v>8577</v>
       </c>
       <c r="B25" s="2">
-        <v>12560</v>
+        <v>18157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D25" s="2">
         <v>39</v>
@@ -1375,27 +1392,27 @@
         <v>41</v>
       </c>
       <c r="F25" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G25" s="5">
-        <v>46300</v>
+        <v>46316</v>
       </c>
       <c r="H25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>8568</v>
+        <v>8578</v>
       </c>
       <c r="B26" s="2">
-        <v>18047</v>
+        <v>18158</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D26" s="2">
         <v>39</v>
@@ -1407,7 +1424,7 @@
         <v>100</v>
       </c>
       <c r="G26" s="5">
-        <v>46304</v>
+        <v>46316</v>
       </c>
       <c r="H26" s="2">
         <v>2</v>
@@ -1418,13 +1435,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>8571</v>
+        <v>8579</v>
       </c>
       <c r="B27" s="2">
-        <v>18171</v>
+        <v>18160</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D27" s="2">
         <v>39</v>
@@ -1436,7 +1453,7 @@
         <v>100</v>
       </c>
       <c r="G27" s="5">
-        <v>46304</v>
+        <v>46316</v>
       </c>
       <c r="H27" s="2">
         <v>2</v>
@@ -1447,13 +1464,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>8572</v>
+        <v>8580</v>
       </c>
       <c r="B28" s="2">
-        <v>18177</v>
+        <v>18161</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D28" s="2">
         <v>39</v>
@@ -1465,7 +1482,7 @@
         <v>100</v>
       </c>
       <c r="G28" s="5">
-        <v>46304</v>
+        <v>46316</v>
       </c>
       <c r="H28" s="2">
         <v>2</v>
@@ -1476,13 +1493,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>8573</v>
+        <v>8581</v>
       </c>
       <c r="B29" s="2">
-        <v>18059</v>
+        <v>18162</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D29" s="2">
         <v>39</v>
@@ -1494,7 +1511,7 @@
         <v>100</v>
       </c>
       <c r="G29" s="5">
-        <v>46304</v>
+        <v>46316</v>
       </c>
       <c r="H29" s="2">
         <v>2</v>
@@ -1505,13 +1522,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>8574</v>
+        <v>8582</v>
       </c>
       <c r="B30" s="2">
-        <v>18173</v>
+        <v>18048</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D30" s="2">
         <v>39</v>
@@ -1523,7 +1540,7 @@
         <v>100</v>
       </c>
       <c r="G30" s="5">
-        <v>46304</v>
+        <v>46316</v>
       </c>
       <c r="H30" s="2">
         <v>2</v>
@@ -1534,13 +1551,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>8575</v>
+        <v>8583</v>
       </c>
       <c r="B31" s="2">
-        <v>18175</v>
+        <v>18180</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D31" s="2">
         <v>39</v>
@@ -1549,27 +1566,27 @@
         <v>41</v>
       </c>
       <c r="F31" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G31" s="5">
         <v>46304</v>
       </c>
       <c r="H31" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>8576</v>
+        <v>8584</v>
       </c>
       <c r="B32" s="2">
-        <v>18163</v>
+        <v>18039</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D32" s="2">
         <v>39</v>
@@ -1581,24 +1598,24 @@
         <v>100</v>
       </c>
       <c r="G32" s="5">
-        <v>46304</v>
+        <v>46317</v>
       </c>
       <c r="H32" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>8577</v>
+        <v>8585</v>
       </c>
       <c r="B33" s="2">
-        <v>18157</v>
+        <v>18041</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D33" s="2">
         <v>39</v>
@@ -1610,7 +1627,7 @@
         <v>100</v>
       </c>
       <c r="G33" s="5">
-        <v>46304</v>
+        <v>46317</v>
       </c>
       <c r="H33" s="2">
         <v>13</v>
@@ -1621,13 +1638,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>8578</v>
+        <v>8586</v>
       </c>
       <c r="B34" s="2">
-        <v>18158</v>
+        <v>18198</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D34" s="2">
         <v>39</v>
@@ -1636,27 +1653,27 @@
         <v>41</v>
       </c>
       <c r="F34" s="4">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G34" s="5">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="H34" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>8579</v>
+        <v>8597</v>
       </c>
       <c r="B35" s="2">
-        <v>18160</v>
+        <v>17899</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D35" s="2">
         <v>39</v>
@@ -1665,56 +1682,56 @@
         <v>41</v>
       </c>
       <c r="F35" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G35" s="5">
         <v>46304</v>
       </c>
       <c r="H35" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>8580</v>
+        <v>8598</v>
       </c>
       <c r="B36" s="2">
-        <v>18161</v>
+        <v>17918</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="2">
+        <v>39</v>
+      </c>
+      <c r="E36" s="2">
+        <v>41</v>
+      </c>
+      <c r="F36" s="4">
         <v>40</v>
-      </c>
-      <c r="D36" s="2">
-        <v>39</v>
-      </c>
-      <c r="E36" s="2">
-        <v>41</v>
-      </c>
-      <c r="F36" s="4">
-        <v>100</v>
       </c>
       <c r="G36" s="5">
         <v>46304</v>
       </c>
       <c r="H36" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>8581</v>
+        <v>8599</v>
       </c>
       <c r="B37" s="2">
-        <v>18162</v>
+        <v>18012</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D37" s="2">
         <v>39</v>
@@ -1729,21 +1746,21 @@
         <v>46304</v>
       </c>
       <c r="H37" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>8582</v>
+        <v>8601</v>
       </c>
       <c r="B38" s="2">
-        <v>18048</v>
+        <v>18214</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D38" s="2">
         <v>39</v>
@@ -1755,24 +1772,24 @@
         <v>100</v>
       </c>
       <c r="G38" s="5">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="H38" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>8583</v>
+        <v>8602</v>
       </c>
       <c r="B39" s="2">
-        <v>18180</v>
+        <v>17900</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D39" s="2">
         <v>39</v>
@@ -1781,10 +1798,10 @@
         <v>41</v>
       </c>
       <c r="F39" s="4">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="G39" s="5">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="H39" s="2">
         <v>6</v>
@@ -1795,13 +1812,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>8584</v>
+        <v>8633</v>
       </c>
       <c r="B40" s="2">
-        <v>18039</v>
+        <v>15212</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D40" s="2">
         <v>39</v>
@@ -1810,27 +1827,27 @@
         <v>41</v>
       </c>
       <c r="F40" s="4">
-        <v>100</v>
+        <v>528</v>
       </c>
       <c r="G40" s="5">
-        <v>46304</v>
+        <v>46324</v>
       </c>
       <c r="H40" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>8585</v>
+        <v>8634</v>
       </c>
       <c r="B41" s="2">
-        <v>18041</v>
+        <v>11845</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D41" s="2">
         <v>39</v>
@@ -1839,27 +1856,27 @@
         <v>41</v>
       </c>
       <c r="F41" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G41" s="5">
-        <v>46304</v>
+        <v>46324</v>
       </c>
       <c r="H41" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>8586</v>
+        <v>8635</v>
       </c>
       <c r="B42" s="2">
-        <v>18198</v>
+        <v>17271</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D42" s="2">
         <v>39</v>
@@ -1868,27 +1885,27 @@
         <v>41</v>
       </c>
       <c r="F42" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G42" s="5">
-        <v>46303</v>
+        <v>46316</v>
       </c>
       <c r="H42" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>8597</v>
+        <v>8637</v>
       </c>
       <c r="B43" s="2">
-        <v>17899</v>
+        <v>17322</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D43" s="2">
         <v>39</v>
@@ -1897,27 +1914,27 @@
         <v>41</v>
       </c>
       <c r="F43" s="4">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="G43" s="5">
-        <v>46304</v>
+        <v>46324</v>
       </c>
       <c r="H43" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>8598</v>
+        <v>8638</v>
       </c>
       <c r="B44" s="2">
-        <v>17918</v>
+        <v>17420</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="D44" s="2">
         <v>39</v>
@@ -1926,27 +1943,27 @@
         <v>41</v>
       </c>
       <c r="F44" s="4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="G44" s="5">
-        <v>46304</v>
+        <v>46318</v>
       </c>
       <c r="H44" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>8599</v>
+        <v>8639</v>
       </c>
       <c r="B45" s="2">
-        <v>18012</v>
+        <v>15535</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D45" s="2">
         <v>39</v>
@@ -1955,27 +1972,27 @@
         <v>41</v>
       </c>
       <c r="F45" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G45" s="5">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="H45" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>8601</v>
+        <v>8702</v>
       </c>
       <c r="B46" s="2">
-        <v>18214</v>
+        <v>18230</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D46" s="2">
         <v>39</v>
@@ -1984,27 +2001,27 @@
         <v>41</v>
       </c>
       <c r="F46" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G46" s="5">
-        <v>46307</v>
+        <v>46317</v>
       </c>
       <c r="H46" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>8602</v>
+        <v>8703</v>
       </c>
       <c r="B47" s="2">
-        <v>17900</v>
+        <v>18232</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D47" s="2">
         <v>39</v>
@@ -2016,24 +2033,24 @@
         <v>40</v>
       </c>
       <c r="G47" s="5">
-        <v>46307</v>
+        <v>46317</v>
       </c>
       <c r="H47" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>8633</v>
+        <v>8704</v>
       </c>
       <c r="B48" s="2">
-        <v>15212</v>
+        <v>18228</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="D48" s="2">
         <v>39</v>
@@ -2042,27 +2059,27 @@
         <v>41</v>
       </c>
       <c r="F48" s="4">
-        <v>528</v>
+        <v>40</v>
       </c>
       <c r="G48" s="5">
-        <v>46308</v>
+        <v>46317</v>
       </c>
       <c r="H48" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>8634</v>
+        <v>8705</v>
       </c>
       <c r="B49" s="2">
-        <v>11845</v>
+        <v>18226</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D49" s="2">
         <v>39</v>
@@ -2071,27 +2088,27 @@
         <v>41</v>
       </c>
       <c r="F49" s="4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="G49" s="5">
-        <v>46308</v>
+        <v>46317</v>
       </c>
       <c r="H49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>8635</v>
+        <v>8707</v>
       </c>
       <c r="B50" s="2">
-        <v>17271</v>
+        <v>18233</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D50" s="2">
         <v>39</v>
@@ -2100,27 +2117,27 @@
         <v>41</v>
       </c>
       <c r="F50" s="4">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="G50" s="5">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="H50" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>8637</v>
+        <v>8762</v>
       </c>
       <c r="B51" s="2">
-        <v>17322</v>
+        <v>18258</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D51" s="2">
         <v>39</v>
@@ -2129,10 +2146,10 @@
         <v>41</v>
       </c>
       <c r="F51" s="4">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="G51" s="5">
-        <v>46309</v>
+        <v>46318</v>
       </c>
       <c r="H51" s="2">
         <v>13</v>
@@ -2143,13 +2160,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>8638</v>
+        <v>8763</v>
       </c>
       <c r="B52" s="2">
-        <v>17420</v>
+        <v>18252</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="D52" s="2">
         <v>39</v>
@@ -2158,10 +2175,10 @@
         <v>41</v>
       </c>
       <c r="F52" s="4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="G52" s="5">
-        <v>46309</v>
+        <v>46318</v>
       </c>
       <c r="H52" s="2">
         <v>13</v>
@@ -2172,13 +2189,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>8639</v>
+        <v>8764</v>
       </c>
       <c r="B53" s="2">
-        <v>15535</v>
+        <v>18254</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D53" s="2">
         <v>39</v>
@@ -2187,27 +2204,27 @@
         <v>41</v>
       </c>
       <c r="F53" s="4">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="G53" s="5">
-        <v>46309</v>
+        <v>46318</v>
       </c>
       <c r="H53" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>8641</v>
+        <v>8765</v>
       </c>
       <c r="B54" s="2">
-        <v>16605</v>
+        <v>18256</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D54" s="2">
         <v>39</v>
@@ -2216,27 +2233,27 @@
         <v>41</v>
       </c>
       <c r="F54" s="4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="G54" s="5">
-        <v>46309</v>
+        <v>46318</v>
       </c>
       <c r="H54" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>8644</v>
+        <v>8780</v>
       </c>
       <c r="B55" s="2">
-        <v>16650</v>
+        <v>17615</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D55" s="2">
         <v>39</v>
@@ -2245,10 +2262,10 @@
         <v>41</v>
       </c>
       <c r="F55" s="4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="G55" s="5">
-        <v>46309</v>
+        <v>46321</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2259,13 +2276,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>8702</v>
+        <v>8781</v>
       </c>
       <c r="B56" s="2">
-        <v>18230</v>
+        <v>30095</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D56" s="2">
         <v>39</v>
@@ -2274,10 +2291,10 @@
         <v>41</v>
       </c>
       <c r="F56" s="4">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="G56" s="5">
-        <v>46311</v>
+        <v>46322</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
@@ -2288,13 +2305,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>8703</v>
+        <v>8782</v>
       </c>
       <c r="B57" s="2">
-        <v>18232</v>
+        <v>16503</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D57" s="2">
         <v>39</v>
@@ -2303,10 +2320,10 @@
         <v>41</v>
       </c>
       <c r="F57" s="4">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="G57" s="5">
-        <v>46311</v>
+        <v>46322</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2317,13 +2334,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>8704</v>
+        <v>8783</v>
       </c>
       <c r="B58" s="2">
-        <v>18228</v>
+        <v>12397</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D58" s="2">
         <v>39</v>
@@ -2332,10 +2349,10 @@
         <v>41</v>
       </c>
       <c r="F58" s="4">
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="G58" s="5">
-        <v>46311</v>
+        <v>46322</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -2346,13 +2363,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>8705</v>
+        <v>8784</v>
       </c>
       <c r="B59" s="2">
-        <v>18226</v>
+        <v>16577</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D59" s="2">
         <v>39</v>
@@ -2361,10 +2378,10 @@
         <v>41</v>
       </c>
       <c r="F59" s="4">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="G59" s="5">
-        <v>46311</v>
+        <v>46322</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -2375,13 +2392,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>8707</v>
+        <v>8785</v>
       </c>
       <c r="B60" s="2">
-        <v>18233</v>
+        <v>16466</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="D60" s="2">
         <v>39</v>
@@ -2390,15 +2407,73 @@
         <v>41</v>
       </c>
       <c r="F60" s="4">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="G60" s="5">
-        <v>46311</v>
+        <v>46322</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>
       </c>
       <c r="I60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>8786</v>
+      </c>
+      <c r="B61" s="2">
+        <v>14145</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" s="2">
+        <v>39</v>
+      </c>
+      <c r="E61" s="2">
+        <v>41</v>
+      </c>
+      <c r="F61" s="4">
+        <v>400</v>
+      </c>
+      <c r="G61" s="5">
+        <v>46322</v>
+      </c>
+      <c r="H61" s="2">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>8787</v>
+      </c>
+      <c r="B62" s="2">
+        <v>15656</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" s="2">
+        <v>39</v>
+      </c>
+      <c r="E62" s="2">
+        <v>41</v>
+      </c>
+      <c r="F62" s="4">
+        <v>200</v>
+      </c>
+      <c r="G62" s="5">
+        <v>46322</v>
+      </c>
+      <c r="H62" s="2">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/data-source/ordens.xlsx
+++ b/data-source/ordens.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/STK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{6DE2805D-EA3C-45B6-A79D-74D904DFFEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A2FA923-49C6-47C0-AF35-5AAEE481C6F2}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{6DE2805D-EA3C-45B6-A79D-74D904DFFEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{926424BB-9EA7-443A-82B2-3417C5C17FB6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="57">
   <si>
     <t>Nro.OP</t>
   </si>
@@ -64,30 +64,18 @@
     <t/>
   </si>
   <si>
-    <t>BORGONHA OURO LIGHT</t>
-  </si>
-  <si>
     <t>JUMBO 1</t>
   </si>
   <si>
-    <t>METALIZADO LAS VEGAS OURO LIGHT</t>
-  </si>
-  <si>
     <t>MIRAGE OURO LIGHT</t>
   </si>
   <si>
     <t>DELHI GLAM PRATA</t>
   </si>
   <si>
-    <t>DENVER PRETO</t>
-  </si>
-  <si>
     <t>SAVOY GLAM OURO LIGHT</t>
   </si>
   <si>
-    <t>SAVOY LUX BRANCO</t>
-  </si>
-  <si>
     <t>DOHA OURO LIGHT</t>
   </si>
   <si>
@@ -97,30 +85,6 @@
     <t>GR 1</t>
   </si>
   <si>
-    <t>BORGONHA TITANIO</t>
-  </si>
-  <si>
-    <t>NAPA LINHO DAKAR NATURAL</t>
-  </si>
-  <si>
-    <t>ARUBA BEGE</t>
-  </si>
-  <si>
-    <t>ARUBA CAMOMILA</t>
-  </si>
-  <si>
-    <t>ARUBA CONHAQUE</t>
-  </si>
-  <si>
-    <t>ARUBA CANELA</t>
-  </si>
-  <si>
-    <t>ARUBA ESPRESSO</t>
-  </si>
-  <si>
-    <t>ARUBA PRETO</t>
-  </si>
-  <si>
     <t>JACARTA PRATA</t>
   </si>
   <si>
@@ -136,30 +100,12 @@
     <t>JACARTA BRONZE</t>
   </si>
   <si>
-    <t>JACARTA PRETO</t>
-  </si>
-  <si>
-    <t>SEVILLA ESPRESSO</t>
-  </si>
-  <si>
-    <t>LILLY CAMOMILA</t>
-  </si>
-  <si>
-    <t>LILLY GUAVA</t>
-  </si>
-  <si>
-    <t>NAPA METAL LYON GRAFITE</t>
-  </si>
-  <si>
     <t>NAPA MADRID ESPRESSO</t>
   </si>
   <si>
     <t>NAPA MADRID CAMOMILA</t>
   </si>
   <si>
-    <t>NAPA MADRID NEVOA</t>
-  </si>
-  <si>
     <t>NAPA MADRID SALVIA</t>
   </si>
   <si>
@@ -190,18 +136,9 @@
     <t>CANYON LIMONCELLO</t>
   </si>
   <si>
-    <t>CORDOBA BEGE</t>
-  </si>
-  <si>
     <t>ESTAM</t>
   </si>
   <si>
-    <t>REC2</t>
-  </si>
-  <si>
-    <t>CANYON CONHAQUE</t>
-  </si>
-  <si>
     <t>MACKAY GLAM OURO LIGHT</t>
   </si>
   <si>
@@ -211,39 +148,15 @@
     <t>OREGON OFF WHITE</t>
   </si>
   <si>
-    <t>OREGON BEGE</t>
-  </si>
-  <si>
-    <t>OREGON CONHAQUE</t>
-  </si>
-  <si>
-    <t>OREGON CAFE</t>
-  </si>
-  <si>
-    <t>OREGON PRETO</t>
-  </si>
-  <si>
     <t>CANYON CAMOMILA</t>
   </si>
   <si>
     <t>CANYON SALVIA</t>
   </si>
   <si>
-    <t>CANYON GUAVA</t>
-  </si>
-  <si>
     <t>CANYON ESPRESSO</t>
   </si>
   <si>
-    <t>BORGONHA WHISKY</t>
-  </si>
-  <si>
-    <t>CANYON CANELA</t>
-  </si>
-  <si>
-    <t>LILLY BRANCO</t>
-  </si>
-  <si>
     <t>SAVOY GLAM PRATA</t>
   </si>
   <si>
@@ -251,6 +164,36 @@
   </si>
   <si>
     <t>STELLAR ROSE</t>
+  </si>
+  <si>
+    <t>IBIZA LASER ROSE</t>
+  </si>
+  <si>
+    <t>BORGONHA GRAFITE</t>
+  </si>
+  <si>
+    <t>NAPA FLOATER VENEZIA DOURADO</t>
+  </si>
+  <si>
+    <t>MADISON CAFE</t>
+  </si>
+  <si>
+    <t>MADISON PRETO</t>
+  </si>
+  <si>
+    <t>MADISON OFF WHITE</t>
+  </si>
+  <si>
+    <t>ASPEN PRETO</t>
+  </si>
+  <si>
+    <t>MAIORCA CARAMELO</t>
+  </si>
+  <si>
+    <t>NAPA MADRID CARAMELO - PU 0.9MM</t>
+  </si>
+  <si>
+    <t>MAIORCA PRETO</t>
   </si>
 </sst>
 </file>
@@ -339,10 +282,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -669,7 +608,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
@@ -716,7 +655,7 @@
         <v>16630</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2">
         <v>39</v>
@@ -745,7 +684,7 @@
         <v>17183</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D3" s="2">
         <v>39</v>
@@ -774,7 +713,7 @@
         <v>14180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2">
         <v>39</v>
@@ -803,7 +742,7 @@
         <v>12879</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2">
         <v>39</v>
@@ -832,7 +771,7 @@
         <v>12883</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D6" s="2">
         <v>39</v>
@@ -861,7 +800,7 @@
         <v>12776</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2">
         <v>39</v>
@@ -890,7 +829,7 @@
         <v>12878</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2">
         <v>39</v>
@@ -919,7 +858,7 @@
         <v>16475</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D9" s="2">
         <v>39</v>
@@ -942,13 +881,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>7934</v>
+        <v>8365</v>
       </c>
       <c r="B10" s="2">
-        <v>13167</v>
+        <v>18014</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2">
         <v>39</v>
@@ -957,39 +896,39 @@
         <v>41</v>
       </c>
       <c r="F10" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G10" s="5">
-        <v>46258</v>
+        <v>46294</v>
       </c>
       <c r="H10" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>8292</v>
+        <v>8499</v>
       </c>
       <c r="B11" s="2">
-        <v>11845</v>
+        <v>20081</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D11" s="2">
         <v>39</v>
       </c>
       <c r="E11" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="4">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="G11" s="5">
-        <v>46287</v>
+        <v>46297</v>
       </c>
       <c r="H11" s="2">
         <v>10</v>
@@ -1000,13 +939,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>8365</v>
+        <v>8527</v>
       </c>
       <c r="B12" s="2">
-        <v>18014</v>
+        <v>15534</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2">
         <v>39</v>
@@ -1015,27 +954,27 @@
         <v>41</v>
       </c>
       <c r="F12" s="4">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="G12" s="5">
-        <v>46294</v>
+        <v>46318</v>
       </c>
       <c r="H12" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>8383</v>
+        <v>8577</v>
       </c>
       <c r="B13" s="2">
-        <v>17425</v>
+        <v>18157</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" s="2">
         <v>39</v>
@@ -1044,27 +983,27 @@
         <v>41</v>
       </c>
       <c r="F13" s="4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G13" s="5">
-        <v>46315</v>
+        <v>46321</v>
       </c>
       <c r="H13" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>8388</v>
+        <v>8578</v>
       </c>
       <c r="B14" s="2">
-        <v>16571</v>
+        <v>18158</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="2">
         <v>39</v>
@@ -1073,27 +1012,27 @@
         <v>41</v>
       </c>
       <c r="F14" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G14" s="5">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="H14" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>8438</v>
+        <v>8579</v>
       </c>
       <c r="B15" s="2">
-        <v>17615</v>
+        <v>18160</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="2">
         <v>39</v>
@@ -1102,56 +1041,56 @@
         <v>41</v>
       </c>
       <c r="F15" s="4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G15" s="5">
-        <v>46295</v>
+        <v>46321</v>
       </c>
       <c r="H15" s="2">
         <v>7</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>8499</v>
+        <v>8580</v>
       </c>
       <c r="B16" s="2">
-        <v>20081</v>
+        <v>18161</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="2">
         <v>39</v>
       </c>
       <c r="E16" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F16" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G16" s="5">
-        <v>46297</v>
+        <v>46321</v>
       </c>
       <c r="H16" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>8527</v>
+        <v>8581</v>
       </c>
       <c r="B17" s="2">
-        <v>15534</v>
+        <v>18162</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D17" s="2">
         <v>39</v>
@@ -1160,24 +1099,24 @@
         <v>41</v>
       </c>
       <c r="F17" s="4">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="G17" s="5">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="H17" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>8530</v>
+        <v>8597</v>
       </c>
       <c r="B18" s="2">
-        <v>13144</v>
+        <v>17899</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>25</v>
@@ -1189,24 +1128,24 @@
         <v>41</v>
       </c>
       <c r="F18" s="4">
-        <v>1668</v>
+        <v>40</v>
       </c>
       <c r="G18" s="5">
         <v>46304</v>
       </c>
       <c r="H18" s="2">
+        <v>6</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>8571</v>
+        <v>8598</v>
       </c>
       <c r="B19" s="2">
-        <v>18171</v>
+        <v>17918</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>26</v>
@@ -1218,24 +1157,24 @@
         <v>41</v>
       </c>
       <c r="F19" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G19" s="5">
-        <v>46318</v>
+        <v>46304</v>
       </c>
       <c r="H19" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>8572</v>
+        <v>8601</v>
       </c>
       <c r="B20" s="2">
-        <v>18177</v>
+        <v>18214</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>27</v>
@@ -1250,21 +1189,21 @@
         <v>100</v>
       </c>
       <c r="G20" s="5">
-        <v>46318</v>
+        <v>46307</v>
       </c>
       <c r="H20" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>8573</v>
+        <v>8602</v>
       </c>
       <c r="B21" s="2">
-        <v>18059</v>
+        <v>17900</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>28</v>
@@ -1276,27 +1215,27 @@
         <v>41</v>
       </c>
       <c r="F21" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G21" s="5">
-        <v>46318</v>
+        <v>46307</v>
       </c>
       <c r="H21" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>8574</v>
+        <v>8637</v>
       </c>
       <c r="B22" s="2">
-        <v>18173</v>
+        <v>17322</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D22" s="2">
         <v>39</v>
@@ -1305,27 +1244,27 @@
         <v>41</v>
       </c>
       <c r="F22" s="4">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G22" s="5">
-        <v>46304</v>
+        <v>46324</v>
       </c>
       <c r="H22" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>8575</v>
+        <v>8639</v>
       </c>
       <c r="B23" s="2">
-        <v>18175</v>
+        <v>15535</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D23" s="2">
         <v>39</v>
@@ -1334,10 +1273,10 @@
         <v>41</v>
       </c>
       <c r="F23" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G23" s="5">
-        <v>46318</v>
+        <v>46309</v>
       </c>
       <c r="H23" s="2">
         <v>2</v>
@@ -1348,13 +1287,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>8576</v>
+        <v>8702</v>
       </c>
       <c r="B24" s="2">
-        <v>18163</v>
+        <v>18230</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2">
         <v>39</v>
@@ -1363,10 +1302,10 @@
         <v>41</v>
       </c>
       <c r="F24" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G24" s="5">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="H24" s="2">
         <v>2</v>
@@ -1377,13 +1316,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>8577</v>
+        <v>8762</v>
       </c>
       <c r="B25" s="2">
-        <v>18157</v>
+        <v>18258</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D25" s="2">
         <v>39</v>
@@ -1392,27 +1331,27 @@
         <v>41</v>
       </c>
       <c r="F25" s="4">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="G25" s="5">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="H25" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>8578</v>
+        <v>8763</v>
       </c>
       <c r="B26" s="2">
-        <v>18158</v>
+        <v>18252</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D26" s="2">
         <v>39</v>
@@ -1421,27 +1360,27 @@
         <v>41</v>
       </c>
       <c r="F26" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G26" s="5">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="H26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>8579</v>
+        <v>8765</v>
       </c>
       <c r="B27" s="2">
-        <v>18160</v>
+        <v>18256</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D27" s="2">
         <v>39</v>
@@ -1450,10 +1389,10 @@
         <v>41</v>
       </c>
       <c r="F27" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G27" s="5">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="H27" s="2">
         <v>2</v>
@@ -1464,13 +1403,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>8580</v>
+        <v>8780</v>
       </c>
       <c r="B28" s="2">
-        <v>18161</v>
+        <v>17615</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D28" s="2">
         <v>39</v>
@@ -1479,27 +1418,27 @@
         <v>41</v>
       </c>
       <c r="F28" s="4">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G28" s="5">
-        <v>46316</v>
+        <v>46322</v>
       </c>
       <c r="H28" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>8581</v>
+        <v>8784</v>
       </c>
       <c r="B29" s="2">
-        <v>18162</v>
+        <v>16577</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D29" s="2">
         <v>39</v>
@@ -1508,56 +1447,56 @@
         <v>41</v>
       </c>
       <c r="F29" s="4">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G29" s="5">
-        <v>46316</v>
+        <v>46325</v>
       </c>
       <c r="H29" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>8582</v>
+        <v>8785</v>
       </c>
       <c r="B30" s="2">
-        <v>18048</v>
+        <v>16466</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="2">
+        <v>39</v>
+      </c>
+      <c r="E30" s="2">
+        <v>41</v>
+      </c>
+      <c r="F30" s="4">
+        <v>310</v>
+      </c>
+      <c r="G30" s="5">
+        <v>46324</v>
+      </c>
+      <c r="H30" s="2">
+        <v>7</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="D30" s="2">
-        <v>39</v>
-      </c>
-      <c r="E30" s="2">
-        <v>41</v>
-      </c>
-      <c r="F30" s="4">
-        <v>100</v>
-      </c>
-      <c r="G30" s="5">
-        <v>46316</v>
-      </c>
-      <c r="H30" s="2">
-        <v>2</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>8583</v>
+        <v>8786</v>
       </c>
       <c r="B31" s="2">
-        <v>18180</v>
+        <v>14145</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D31" s="2">
         <v>39</v>
@@ -1566,27 +1505,27 @@
         <v>41</v>
       </c>
       <c r="F31" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G31" s="5">
-        <v>46304</v>
+        <v>46324</v>
       </c>
       <c r="H31" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>8584</v>
+        <v>8787</v>
       </c>
       <c r="B32" s="2">
-        <v>18039</v>
+        <v>15656</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D32" s="2">
         <v>39</v>
@@ -1595,27 +1534,27 @@
         <v>41</v>
       </c>
       <c r="F32" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G32" s="5">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="H32" s="2">
         <v>13</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>8585</v>
+        <v>8798</v>
       </c>
       <c r="B33" s="2">
-        <v>18041</v>
+        <v>17224</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D33" s="2">
         <v>39</v>
@@ -1624,27 +1563,27 @@
         <v>41</v>
       </c>
       <c r="F33" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G33" s="5">
-        <v>46317</v>
+        <v>46323</v>
       </c>
       <c r="H33" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>8586</v>
+        <v>8810</v>
       </c>
       <c r="B34" s="2">
-        <v>18198</v>
+        <v>11847</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D34" s="2">
         <v>39</v>
@@ -1656,24 +1595,24 @@
         <v>400</v>
       </c>
       <c r="G34" s="5">
-        <v>46303</v>
+        <v>46324</v>
       </c>
       <c r="H34" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>8597</v>
+        <v>8812</v>
       </c>
       <c r="B35" s="2">
-        <v>17899</v>
+        <v>16605</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D35" s="2">
         <v>39</v>
@@ -1682,24 +1621,24 @@
         <v>41</v>
       </c>
       <c r="F35" s="4">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="G35" s="5">
-        <v>46304</v>
+        <v>46324</v>
       </c>
       <c r="H35" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>8598</v>
+        <v>8819</v>
       </c>
       <c r="B36" s="2">
-        <v>17918</v>
+        <v>18256</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>43</v>
@@ -1711,27 +1650,27 @@
         <v>41</v>
       </c>
       <c r="F36" s="4">
-        <v>40</v>
+        <v>6.6</v>
       </c>
       <c r="G36" s="5">
-        <v>46304</v>
+        <v>46322</v>
       </c>
       <c r="H36" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>8599</v>
+        <v>8834</v>
       </c>
       <c r="B37" s="2">
-        <v>18012</v>
+        <v>17307</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D37" s="2">
         <v>39</v>
@@ -1740,27 +1679,27 @@
         <v>41</v>
       </c>
       <c r="F37" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G37" s="5">
-        <v>46304</v>
+        <v>46325</v>
       </c>
       <c r="H37" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>8601</v>
+        <v>8835</v>
       </c>
       <c r="B38" s="2">
-        <v>18214</v>
+        <v>17308</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D38" s="2">
         <v>39</v>
@@ -1769,27 +1708,27 @@
         <v>41</v>
       </c>
       <c r="F38" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G38" s="5">
-        <v>46307</v>
+        <v>46325</v>
       </c>
       <c r="H38" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>8602</v>
+        <v>8836</v>
       </c>
       <c r="B39" s="2">
-        <v>17900</v>
+        <v>17306</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D39" s="2">
         <v>39</v>
@@ -1798,27 +1737,27 @@
         <v>41</v>
       </c>
       <c r="F39" s="4">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="G39" s="5">
-        <v>46307</v>
+        <v>46325</v>
       </c>
       <c r="H39" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>8633</v>
+        <v>8841</v>
       </c>
       <c r="B40" s="2">
-        <v>15212</v>
+        <v>18336</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D40" s="2">
         <v>39</v>
@@ -1827,27 +1766,27 @@
         <v>41</v>
       </c>
       <c r="F40" s="4">
-        <v>528</v>
+        <v>40</v>
       </c>
       <c r="G40" s="5">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="H40" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>8634</v>
+        <v>8853</v>
       </c>
       <c r="B41" s="2">
-        <v>11845</v>
+        <v>11784</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D41" s="2">
         <v>39</v>
@@ -1856,56 +1795,56 @@
         <v>41</v>
       </c>
       <c r="F41" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="G41" s="5">
-        <v>46324</v>
+        <v>46329</v>
       </c>
       <c r="H41" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>8635</v>
+        <v>8853</v>
       </c>
       <c r="B42" s="2">
-        <v>17271</v>
+        <v>11905</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2">
         <v>39</v>
       </c>
       <c r="E42" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F42" s="4">
         <v>200</v>
       </c>
       <c r="G42" s="5">
-        <v>46316</v>
+        <v>46329</v>
       </c>
       <c r="H42" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>8637</v>
+        <v>8854</v>
       </c>
       <c r="B43" s="2">
-        <v>17322</v>
+        <v>11785</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D43" s="2">
         <v>39</v>
@@ -1914,568 +1853,226 @@
         <v>41</v>
       </c>
       <c r="F43" s="4">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G43" s="5">
-        <v>46324</v>
+        <v>46329</v>
       </c>
       <c r="H43" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
-        <v>8638</v>
-      </c>
-      <c r="B44" s="2">
-        <v>17420</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="2">
-        <v>39</v>
-      </c>
-      <c r="E44" s="2">
-        <v>41</v>
-      </c>
-      <c r="F44" s="4">
-        <v>1000</v>
-      </c>
-      <c r="G44" s="5">
-        <v>46318</v>
-      </c>
-      <c r="H44" s="2">
-        <v>6</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="3"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
-        <v>8639</v>
-      </c>
-      <c r="B45" s="2">
-        <v>15535</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D45" s="2">
-        <v>39</v>
-      </c>
-      <c r="E45" s="2">
-        <v>41</v>
-      </c>
-      <c r="F45" s="4">
-        <v>200</v>
-      </c>
-      <c r="G45" s="5">
-        <v>46309</v>
-      </c>
-      <c r="H45" s="2">
-        <v>2</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="3"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
-        <v>8702</v>
-      </c>
-      <c r="B46" s="2">
-        <v>18230</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D46" s="2">
-        <v>39</v>
-      </c>
-      <c r="E46" s="2">
-        <v>41</v>
-      </c>
-      <c r="F46" s="4">
-        <v>40</v>
-      </c>
-      <c r="G46" s="5">
-        <v>46317</v>
-      </c>
-      <c r="H46" s="2">
-        <v>2</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="3"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
-        <v>8703</v>
-      </c>
-      <c r="B47" s="2">
-        <v>18232</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D47" s="2">
-        <v>39</v>
-      </c>
-      <c r="E47" s="2">
-        <v>41</v>
-      </c>
-      <c r="F47" s="4">
-        <v>40</v>
-      </c>
-      <c r="G47" s="5">
-        <v>46317</v>
-      </c>
-      <c r="H47" s="2">
-        <v>2</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="3"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
-        <v>8704</v>
-      </c>
-      <c r="B48" s="2">
-        <v>18228</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D48" s="2">
-        <v>39</v>
-      </c>
-      <c r="E48" s="2">
-        <v>41</v>
-      </c>
-      <c r="F48" s="4">
-        <v>40</v>
-      </c>
-      <c r="G48" s="5">
-        <v>46317</v>
-      </c>
-      <c r="H48" s="2">
-        <v>2</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="3"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
-        <v>8705</v>
-      </c>
-      <c r="B49" s="2">
-        <v>18226</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D49" s="2">
-        <v>39</v>
-      </c>
-      <c r="E49" s="2">
-        <v>41</v>
-      </c>
-      <c r="F49" s="4">
-        <v>40</v>
-      </c>
-      <c r="G49" s="5">
-        <v>46317</v>
-      </c>
-      <c r="H49" s="2">
-        <v>2</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="3"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
-        <v>8707</v>
-      </c>
-      <c r="B50" s="2">
-        <v>18233</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="2">
-        <v>39</v>
-      </c>
-      <c r="E50" s="2">
-        <v>41</v>
-      </c>
-      <c r="F50" s="4">
-        <v>40</v>
-      </c>
-      <c r="G50" s="5">
-        <v>46311</v>
-      </c>
-      <c r="H50" s="2">
-        <v>2</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="3"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
-        <v>8762</v>
-      </c>
-      <c r="B51" s="2">
-        <v>18258</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D51" s="2">
-        <v>39</v>
-      </c>
-      <c r="E51" s="2">
-        <v>41</v>
-      </c>
-      <c r="F51" s="4">
-        <v>40</v>
-      </c>
-      <c r="G51" s="5">
-        <v>46318</v>
-      </c>
-      <c r="H51" s="2">
-        <v>13</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="3"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
-        <v>8763</v>
-      </c>
-      <c r="B52" s="2">
-        <v>18252</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D52" s="2">
-        <v>39</v>
-      </c>
-      <c r="E52" s="2">
-        <v>41</v>
-      </c>
-      <c r="F52" s="4">
-        <v>40</v>
-      </c>
-      <c r="G52" s="5">
-        <v>46318</v>
-      </c>
-      <c r="H52" s="2">
-        <v>13</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="3"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
-        <v>8764</v>
-      </c>
-      <c r="B53" s="2">
-        <v>18254</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D53" s="2">
-        <v>39</v>
-      </c>
-      <c r="E53" s="2">
-        <v>41</v>
-      </c>
-      <c r="F53" s="4">
-        <v>40</v>
-      </c>
-      <c r="G53" s="5">
-        <v>46318</v>
-      </c>
-      <c r="H53" s="2">
-        <v>13</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="3"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
-        <v>8765</v>
-      </c>
-      <c r="B54" s="2">
-        <v>18256</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D54" s="2">
-        <v>39</v>
-      </c>
-      <c r="E54" s="2">
-        <v>41</v>
-      </c>
-      <c r="F54" s="4">
-        <v>40</v>
-      </c>
-      <c r="G54" s="5">
-        <v>46318</v>
-      </c>
-      <c r="H54" s="2">
-        <v>13</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="3"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
-        <v>8780</v>
-      </c>
-      <c r="B55" s="2">
-        <v>17615</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D55" s="2">
-        <v>39</v>
-      </c>
-      <c r="E55" s="2">
-        <v>41</v>
-      </c>
-      <c r="F55" s="4">
-        <v>120</v>
-      </c>
-      <c r="G55" s="5">
-        <v>46321</v>
-      </c>
-      <c r="H55" s="2">
-        <v>0</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="3"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
-        <v>8781</v>
-      </c>
-      <c r="B56" s="2">
-        <v>30095</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D56" s="2">
-        <v>39</v>
-      </c>
-      <c r="E56" s="2">
-        <v>41</v>
-      </c>
-      <c r="F56" s="4">
-        <v>200</v>
-      </c>
-      <c r="G56" s="5">
-        <v>46322</v>
-      </c>
-      <c r="H56" s="2">
-        <v>0</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="3"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
-        <v>8782</v>
-      </c>
-      <c r="B57" s="2">
-        <v>16503</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D57" s="2">
-        <v>39</v>
-      </c>
-      <c r="E57" s="2">
-        <v>41</v>
-      </c>
-      <c r="F57" s="4">
-        <v>400</v>
-      </c>
-      <c r="G57" s="5">
-        <v>46322</v>
-      </c>
-      <c r="H57" s="2">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="3"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="2">
-        <v>8783</v>
-      </c>
-      <c r="B58" s="2">
-        <v>12397</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D58" s="2">
-        <v>39</v>
-      </c>
-      <c r="E58" s="2">
-        <v>41</v>
-      </c>
-      <c r="F58" s="4">
-        <v>181</v>
-      </c>
-      <c r="G58" s="5">
-        <v>46322</v>
-      </c>
-      <c r="H58" s="2">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="3"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="2">
-        <v>8784</v>
-      </c>
-      <c r="B59" s="2">
-        <v>16577</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D59" s="2">
-        <v>39</v>
-      </c>
-      <c r="E59" s="2">
-        <v>41</v>
-      </c>
-      <c r="F59" s="4">
-        <v>400</v>
-      </c>
-      <c r="G59" s="5">
-        <v>46322</v>
-      </c>
-      <c r="H59" s="2">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="3"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="2">
-        <v>8785</v>
-      </c>
-      <c r="B60" s="2">
-        <v>16466</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D60" s="2">
-        <v>39</v>
-      </c>
-      <c r="E60" s="2">
-        <v>41</v>
-      </c>
-      <c r="F60" s="4">
-        <v>400</v>
-      </c>
-      <c r="G60" s="5">
-        <v>46322</v>
-      </c>
-      <c r="H60" s="2">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="3"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="2">
-        <v>8786</v>
-      </c>
-      <c r="B61" s="2">
-        <v>14145</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D61" s="2">
-        <v>39</v>
-      </c>
-      <c r="E61" s="2">
-        <v>41</v>
-      </c>
-      <c r="F61" s="4">
-        <v>400</v>
-      </c>
-      <c r="G61" s="5">
-        <v>46322</v>
-      </c>
-      <c r="H61" s="2">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="3"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="2">
-        <v>8787</v>
-      </c>
-      <c r="B62" s="2">
-        <v>15656</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D62" s="2">
-        <v>39</v>
-      </c>
-      <c r="E62" s="2">
-        <v>41</v>
-      </c>
-      <c r="F62" s="4">
-        <v>200</v>
-      </c>
-      <c r="G62" s="5">
-        <v>46322</v>
-      </c>
-      <c r="H62" s="2">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="3"/>
     </row>
   </sheetData>
   <printOptions gridLines="1"/>
